--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>819.5787030947321</v>
+        <v>819.5830213890927</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>18</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1228.131404319687</v>
+        <v>1266.538779994587</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>12</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>173.1584504905389</v>
+        <v>173.1403986810297</v>
       </c>
       <c r="D77" s="11" t="n">
         <v>12</v>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>216.247697782822</v>
+        <v>223.4636766117221</v>
       </c>
       <c r="D79" s="11" t="n">
         <v>11</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>3701.178470936668</v>
+        <v>3703.984222982135</v>
       </c>
       <c r="D89" s="11" t="n">
         <v>11</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>1106.723584904074</v>
+        <v>1107.408450097416</v>
       </c>
       <c r="D94" s="11" t="n">
         <v>10</v>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>1519.615</v>
+        <v>1519.22375</v>
       </c>
       <c r="D97" s="11" t="n">
         <v>10</v>

--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -731,20 +731,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>51705.97227905274</v>
+        <v>2181.118846802559</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>2</v>
@@ -759,26 +759,26 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>887.31029399802</v>
+        <v>51705.97227905274</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>20</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G11" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -787,26 +787,26 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>2797.56</v>
+        <v>887.31029399802</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>20</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -815,26 +815,26 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>2328.325430974198</v>
+        <v>2797.56</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>20</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -843,26 +843,26 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>467.9592218330383</v>
+        <v>2328.325430974198</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>20</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -871,26 +871,26 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>9426.083715237124</v>
+        <v>467.9592218330383</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>20</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -899,26 +899,26 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>185.5358413472565</v>
+        <v>9426.083715237124</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>20</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -927,23 +927,23 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>1467.773894020386</v>
+        <v>185.5358413472565</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>2</v>
@@ -955,23 +955,23 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>9943.400060189808</v>
+        <v>1467.773894020386</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>2</v>
@@ -983,26 +983,26 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>1436.941013956506</v>
+        <v>9943.400060189808</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1011,26 +1011,26 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>7558.419733256688</v>
+        <v>1436.941013956506</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1039,11 +1039,11 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>819.5830213890927</v>
+        <v>7558.419733256688</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>18</v>
@@ -1052,13 +1052,13 @@
         <v>54</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1067,20 +1067,20 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>5408.66042183927</v>
+        <v>819.5787030947321</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>0</v>
@@ -1095,20 +1095,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>1706.620601753679</v>
+        <v>5408.66042183927</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="11" t="n">
         <v>0</v>
@@ -1123,20 +1123,20 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>2047.518736253673</v>
+        <v>1706.620601753679</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24" s="11" t="n">
         <v>0</v>
@@ -1151,23 +1151,23 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>18070.22634115733</v>
+        <v>2047.518736253673</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" s="11" t="n">
         <v>0</v>
@@ -1179,26 +1179,26 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>5043.706392130815</v>
+        <v>18070.22634115733</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>16</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1207,26 +1207,26 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>773.8516434040006</v>
+        <v>338.5883166014877</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>16</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1235,26 +1235,26 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>317.0615139451737</v>
+        <v>2432.90077277473</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>16</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1263,26 +1263,26 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>1507.43743127076</v>
+        <v>5043.706392130815</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1291,20 +1291,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>643.3129777460049</v>
+        <v>773.8516434040006</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G30" s="11" t="n">
         <v>0</v>
@@ -1319,20 +1319,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>1130.236351390465</v>
+        <v>317.0615139451737</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G31" s="11" t="n">
         <v>0</v>
@@ -1347,20 +1347,20 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>502.5002831428833</v>
+        <v>1507.43743127076</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>15</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>2</v>
@@ -1375,20 +1375,20 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>15693.3081811875</v>
+        <v>643.3129777460049</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G33" s="11" t="n">
         <v>0</v>
@@ -1403,23 +1403,23 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>3887.293793842997</v>
+        <v>1130.236351390465</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" s="11" t="n">
         <v>0</v>
@@ -1431,23 +1431,23 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>2936.826602653458</v>
+        <v>502.5002831428833</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>0</v>
@@ -1459,20 +1459,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>2232.11532814507</v>
+        <v>15693.3081811875</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G36" s="11" t="n">
         <v>0</v>
@@ -1487,23 +1487,23 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>501.3909872436523</v>
+        <v>6326.709393755303</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>0</v>
@@ -1515,23 +1515,23 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>894.035863640597</v>
+        <v>3887.293793842997</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>0</v>
@@ -1543,26 +1543,26 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>734.650899345</v>
+        <v>2936.826602653458</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1571,20 +1571,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>1181.257040614616</v>
+        <v>2232.11532814507</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>0</v>
@@ -1599,20 +1599,20 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>3603.21492857029</v>
+        <v>501.3909872436523</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G41" s="11" t="n">
         <v>0</v>
@@ -1627,20 +1627,20 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>863.284200837561</v>
+        <v>894.035863640597</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>0</v>
@@ -1655,26 +1655,26 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>736.7083057902911</v>
+        <v>734.650899345</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>4040.093804828691</v>
+        <v>1181.257040614616</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G44" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>1590.297106761858</v>
+        <v>3603.21492857029</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>8</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1739,20 +1739,20 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>1503.362868106394</v>
+        <v>863.284200837561</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G46" s="11" t="n">
         <v>0</v>
@@ -1767,26 +1767,26 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>1980.960974884033</v>
+        <v>736.7083057902911</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1795,26 +1795,26 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1266.538779994587</v>
+        <v>4040.093804828691</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1823,20 +1823,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>2453.464980683424</v>
+        <v>495.8551369592285</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G49" s="11" t="n">
         <v>0</v>
@@ -1851,17 +1851,17 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1916.165686626211</v>
+        <v>1590.297106761858</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="F50" s="11" t="n">
         <v>8</v>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1879,23 +1879,23 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>1909.542981688637</v>
+        <v>1503.362868106394</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H51" s="11" t="n">
         <v>0</v>
@@ -1907,26 +1907,26 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>1266.645596845557</v>
+        <v>1980.960974884033</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -1935,26 +1935,26 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>11209.45725709417</v>
+        <v>1228.131404319687</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1963,26 +1963,26 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>50125.16938093872</v>
+        <v>2453.464980683424</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1991,26 +1991,26 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>375.29175761521</v>
+        <v>1916.165686626211</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2019,26 +2019,26 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>888.9226680091321</v>
+        <v>1909.542981688637</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G56" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H56" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2047,26 +2047,26 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>348.2540182817194</v>
+        <v>1266.645596845557</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G57" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2075,26 +2075,26 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>1266.578763183594</v>
+        <v>11209.45725709417</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2103,26 +2103,26 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>1936.685986866843</v>
+        <v>50125.16938093872</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H59" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
@@ -2131,26 +2131,26 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>300.4079095397049</v>
+        <v>375.29175761521</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G60" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H60" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2159,26 +2159,26 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>3582.384955379238</v>
+        <v>888.9226680091321</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2187,23 +2187,23 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>578.2881048514639</v>
+        <v>348.2540182817194</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H62" s="11" t="n">
         <v>0</v>
@@ -2215,17 +2215,17 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>632.3570678411692</v>
+        <v>1266.578763183594</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F63" s="11" t="n">
         <v>2</v>
@@ -2243,26 +2243,26 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ALNY</t>
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>279.098672945</v>
+        <v>310.2096807095181</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G64" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2271,26 +2271,26 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>4413.411313926686</v>
+        <v>1936.685986866843</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G65" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2299,26 +2299,26 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>961.483917092135</v>
+        <v>300.4079095397049</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H66" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2327,20 +2327,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>147.7844691841773</v>
+        <v>3582.384955379238</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G67" s="11" t="n">
         <v>0</v>
@@ -2355,23 +2355,23 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>189.4443948</v>
+        <v>578.2881048514639</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" s="11" t="n">
         <v>0</v>
@@ -2383,20 +2383,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>1692.263411813725</v>
+        <v>632.3570678411692</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G69" s="11" t="n">
         <v>0</v>
@@ -2411,26 +2411,26 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>998.606598641333</v>
+        <v>279.098672945</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2439,23 +2439,23 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>798.7989569220813</v>
+        <v>4413.411313926686</v>
       </c>
       <c r="D71" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G71" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H71" s="11" t="n">
         <v>0</v>
@@ -2467,26 +2467,26 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>238.4795946211766</v>
+        <v>961.483917092135</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G72" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2495,23 +2495,23 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>423.5268401265633</v>
+        <v>147.7844691841773</v>
       </c>
       <c r="D73" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G73" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H73" s="11" t="n">
         <v>0</v>
@@ -2523,20 +2523,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>2117.704080574115</v>
+        <v>189.4443948</v>
       </c>
       <c r="D74" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G74" s="11" t="n">
         <v>0</v>
@@ -2551,26 +2551,26 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>525.2710432918542</v>
+        <v>1692.263411813725</v>
       </c>
       <c r="D75" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G75" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2579,23 +2579,23 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>750.2193542374569</v>
+        <v>998.606598641333</v>
       </c>
       <c r="D76" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" s="11" t="n">
         <v>0</v>
@@ -2607,26 +2607,26 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>173.1403986810297</v>
+        <v>798.7989569220813</v>
       </c>
       <c r="D77" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G77" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H77" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2635,26 +2635,26 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>TPR</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>571.1003572384741</v>
+        <v>238.4795946211766</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G78" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2663,23 +2663,23 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>223.4636766117221</v>
+        <v>423.5268401265633</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G79" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79" s="11" t="n">
         <v>0</v>
@@ -2691,23 +2691,23 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>2297.663392677704</v>
+        <v>2117.704080574115</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H80" s="11" t="n">
         <v>0</v>
@@ -2719,26 +2719,26 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>871.8737591103564</v>
+        <v>525.2710432918542</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G81" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2747,20 +2747,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>556.3774182767152</v>
+        <v>750.2193542374569</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G82" s="11" t="n">
         <v>0</v>
@@ -2775,26 +2775,26 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>2872.029718695297</v>
+        <v>173.1584504905389</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E83" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F83" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="F83" s="11" t="n">
-        <v>19</v>
-      </c>
       <c r="G83" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H83" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2803,20 +2803,20 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>2613.572568166611</v>
+        <v>571.1003572384741</v>
       </c>
       <c r="D84" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G84" s="11" t="n">
         <v>0</v>
@@ -2831,20 +2831,20 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>1756.805907806176</v>
+        <v>216.247697782822</v>
       </c>
       <c r="D85" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G85" s="11" t="n">
         <v>0</v>
@@ -2859,23 +2859,23 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>314.2381241379629</v>
+        <v>2297.663392677704</v>
       </c>
       <c r="D86" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F86" s="11" t="n">
         <v>10</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H86" s="11" t="n">
         <v>0</v>
@@ -2887,23 +2887,23 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>378.7722323021641</v>
+        <v>871.8737591103564</v>
       </c>
       <c r="D87" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="G87" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" s="11" t="n">
         <v>0</v>
@@ -2915,20 +2915,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>159.881705475761</v>
+        <v>556.3774182767152</v>
       </c>
       <c r="D88" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G88" s="11" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>3703.984222982135</v>
+        <v>2872.029718695297</v>
       </c>
       <c r="D89" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G89" s="11" t="n">
         <v>0</v>
@@ -2971,20 +2971,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>8631.711784575</v>
+        <v>2613.572568166611</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G90" s="11" t="n">
         <v>0</v>
@@ -2999,20 +2999,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>652.846464430693</v>
+        <v>1756.805907806176</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G91" s="11" t="n">
         <v>0</v>
@@ -3027,20 +3027,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>972.8830703509864</v>
+        <v>314.2381241379629</v>
       </c>
       <c r="D92" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F92" s="11" t="n">
         <v>10</v>
-      </c>
-      <c r="E92" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="F92" s="11" t="n">
-        <v>12</v>
       </c>
       <c r="G92" s="11" t="n">
         <v>0</v>
@@ -3055,26 +3055,26 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>1024.110311641273</v>
+        <v>378.7722323021641</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G93" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H93" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -3083,26 +3083,26 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>1107.408450097416</v>
+        <v>159.881705475761</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G94" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -3111,26 +3111,26 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>495.8685788761032</v>
+        <v>3701.178470936668</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G95" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3139,20 +3139,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>504.6930349145508</v>
+        <v>8631.711784575</v>
       </c>
       <c r="D96" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>0</v>
@@ -3167,26 +3167,26 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>1519.22375</v>
+        <v>652.846464430693</v>
       </c>
       <c r="D97" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G97" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H97" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -3195,20 +3195,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>879.9082011938476</v>
+        <v>972.8830703509864</v>
       </c>
       <c r="D98" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G98" s="11" t="n">
         <v>0</v>
@@ -3223,26 +3223,26 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>722.1592718621234</v>
+        <v>1024.110311641273</v>
       </c>
       <c r="D99" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H99" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -3251,26 +3251,26 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>746.520495575791</v>
+        <v>1106.723584904074</v>
       </c>
       <c r="D100" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G100" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -3279,26 +3279,26 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>1249.679017327932</v>
+        <v>495.8685788761032</v>
       </c>
       <c r="D101" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G101" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -3307,26 +3307,26 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>868.917837689209</v>
+        <v>504.6930349145508</v>
       </c>
       <c r="D102" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H102" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3335,17 +3335,17 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>809.8413422704602</v>
+        <v>1519.615</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F103" s="11" t="n">
         <v>8</v>
@@ -3354,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3363,23 +3363,23 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>552.9194651205022</v>
+        <v>879.9082011938476</v>
       </c>
       <c r="D104" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H104" s="11" t="n">
         <v>0</v>
@@ -3391,20 +3391,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>2162.917831526948</v>
+        <v>722.1592718621234</v>
       </c>
       <c r="D105" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G105" s="11" t="n">
         <v>0</v>

--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>819.5787030947321</v>
+        <v>819.5830213890927</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>18</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1228.131404319687</v>
+        <v>1266.538779994587</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>12</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>173.1584504905389</v>
+        <v>173.1403986810297</v>
       </c>
       <c r="D83" s="11" t="n">
         <v>12</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>216.247697782822</v>
+        <v>223.4636766117221</v>
       </c>
       <c r="D85" s="11" t="n">
         <v>11</v>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>3701.178470936668</v>
+        <v>3703.984222982135</v>
       </c>
       <c r="D95" s="11" t="n">
         <v>11</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>1106.723584904074</v>
+        <v>1107.408450097416</v>
       </c>
       <c r="D100" s="11" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>1519.615</v>
+        <v>1519.22375</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>10</v>

--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026. 10. 19</t>
+          <t>2026. 10. 20</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>26965.78393</v>
+        <v>28308.68128640267</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>32</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>39284.84751369684</v>
+        <v>39616.77175388506</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>27</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>41653.93459302931</v>
+        <v>42092.98880558862</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>26</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>41203.87388699569</v>
+        <v>41601.34676900319</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>26</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2181.118846802559</v>
+        <v>2200.933076956395</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>22</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>51705.97227905274</v>
+        <v>52420.72141571045</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>20</v>
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>887.31029399802</v>
+        <v>934.8876798875195</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>20</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>2</v>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>2797.56</v>
+        <v>2838.051099853516</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>20</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>2328.325430974198</v>
+        <v>2335.595437098023</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>20</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>467.9592218330383</v>
+        <v>465.616125</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>20</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>9426.083715237124</v>
+        <v>9417.356545948278</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>20</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>185.5358413472565</v>
+        <v>184.6330990637177</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>1467.773894020386</v>
+        <v>1502.821809510193</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>19</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>9943.400060189808</v>
+        <v>10238.24892161437</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>18</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1436.941013956506</v>
+        <v>1428.975041951403</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>18</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>7558.419733256688</v>
+        <v>7564.240061649077</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>18</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>819.5830213890927</v>
+        <v>838.5614921868186</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>18</v>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>5408.66042183927</v>
+        <v>5399.725484029615</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>18</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1706.620601753679</v>
+        <v>1674.333081449292</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>18</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>2047.518736253673</v>
+        <v>2130.738734050154</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>17</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>18070.22634115733</v>
+        <v>17971.12797583497</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>16</v>
@@ -1211,16 +1211,16 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>338.5883166014877</v>
+        <v>337.0991652513536</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>16</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G27" s="11" t="n">
         <v>4</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2432.90077277473</v>
+        <v>2435.57076919723</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>16</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>5043.706392130815</v>
+        <v>4995.287011810465</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>16</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>773.8516434040006</v>
+        <v>780.9429728699999</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>16</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>317.0615139451737</v>
+        <v>311.212410148497</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>16</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>1507.43743127076</v>
+        <v>1530.329779133544</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>15</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>643.3129777460049</v>
+        <v>652.8778904062561</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>15</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>1130.236351390465</v>
+        <v>1142.817542616976</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>15</v>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>502.5002831428833</v>
+        <v>512.9272170357361</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>15</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>15693.3081811875</v>
+        <v>15972.08799048795</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>14</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>6326.709393755303</v>
+        <v>6348.292693211174</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>14</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>3887.293793842997</v>
+        <v>3928.522227972212</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>14</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>2936.826602653458</v>
+        <v>2908.511800149322</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>14</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>2232.11532814507</v>
+        <v>2307.410455026478</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>14</v>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>501.3909872436523</v>
+        <v>503.0629936218262</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>14</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>894.035863640597</v>
+        <v>904.0804225119031</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>14</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>734.650899345</v>
+        <v>728.5659143625229</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>14</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>1181.257040614616</v>
+        <v>1185.349741892308</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>14</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>3603.21492857029</v>
+        <v>3652.133957301473</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>14</v>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>863.284200837561</v>
+        <v>852.8466701664112</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>14</v>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>736.7083057902911</v>
+        <v>726.0911501775</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>14</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>4040.093804828691</v>
+        <v>4019.441424028571</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>14</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>495.8551369592285</v>
+        <v>497.173587748081</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>14</v>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1590.297106761858</v>
+        <v>1549.138964266283</v>
       </c>
       <c r="D50" s="11" t="n">
         <v>14</v>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>1503.362868106394</v>
+        <v>1512.926277811893</v>
       </c>
       <c r="D51" s="11" t="n">
         <v>13</v>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>1980.960974884033</v>
+        <v>1995.363474884033</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>12</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1266.538779994587</v>
+        <v>1259.952384230827</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>12</v>
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>2453.464980683424</v>
+        <v>2419.480789738685</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F54" s="11" t="n">
         <v>14</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1916.165686626211</v>
+        <v>1910.883940803029</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>12</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>1909.542981688637</v>
+        <v>1892.276112668637</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>12</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1266.645596845557</v>
+        <v>1272.247138958054</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>12</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>11209.45725709417</v>
+        <v>11060.62505038597</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>12</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>50125.16938093872</v>
+        <v>50049.28124830322</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>12</v>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>375.29175761521</v>
+        <v>395.1336966608825</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>12</v>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>888.9226680091321</v>
+        <v>867.794179718005</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>12</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>348.2540182817194</v>
+        <v>355.6493893790611</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>12</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1266.578763183594</v>
+        <v>1261.242800415039</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>12</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>310.2096807095181</v>
+        <v>312.1632823984335</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>12</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>1936.685986866843</v>
+        <v>1897.999446575528</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>12</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>300.4079095397049</v>
+        <v>298.4839444397049</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>12</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>3582.384955379238</v>
+        <v>3523.645858443151</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>12</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>578.2881048514639</v>
+        <v>580.4567182869519</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>12</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>632.3570678411692</v>
+        <v>627.8540033123382</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>12</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>279.098672945</v>
+        <v>274.7663912228318</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>12</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>4413.411313926686</v>
+        <v>4401.24917009239</v>
       </c>
       <c r="D71" s="11" t="n">
         <v>12</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>961.483917092135</v>
+        <v>932.5015994401825</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>12</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>147.7844691841773</v>
+        <v>147.4650419468829</v>
       </c>
       <c r="D73" s="11" t="n">
         <v>12</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>189.4443948</v>
+        <v>186.2958081920508</v>
       </c>
       <c r="D74" s="11" t="n">
         <v>12</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>1692.263411813725</v>
+        <v>1682.607663303897</v>
       </c>
       <c r="D75" s="11" t="n">
         <v>12</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>998.606598641333</v>
+        <v>1001.6222222925</v>
       </c>
       <c r="D76" s="11" t="n">
         <v>12</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>798.7989569220813</v>
+        <v>788.75785071</v>
       </c>
       <c r="D77" s="11" t="n">
         <v>12</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>238.4795946211766</v>
+        <v>233.5782392514702</v>
       </c>
       <c r="D78" s="11" t="n">
         <v>12</v>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>423.5268401265633</v>
+        <v>422.6629206554684</v>
       </c>
       <c r="D79" s="11" t="n">
         <v>12</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>2117.704080574115</v>
+        <v>2136.747867325885</v>
       </c>
       <c r="D80" s="11" t="n">
         <v>12</v>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>525.2710432918542</v>
+        <v>520.9668936453644</v>
       </c>
       <c r="D81" s="11" t="n">
         <v>12</v>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>750.2193542374569</v>
+        <v>744.4797001375432</v>
       </c>
       <c r="D82" s="11" t="n">
         <v>12</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>173.1403986810297</v>
+        <v>171.3539231212747</v>
       </c>
       <c r="D83" s="11" t="n">
         <v>12</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>571.1003572384741</v>
+        <v>568.7761878375586</v>
       </c>
       <c r="D84" s="11" t="n">
         <v>11</v>
@@ -2831,23 +2831,23 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>223.4636766117221</v>
+        <v>2320.758543861598</v>
       </c>
       <c r="D85" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F85" s="11" t="n">
         <v>10</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H85" s="11" t="n">
         <v>0</v>
@@ -2859,11 +2859,11 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>2297.663392677704</v>
+        <v>860.865233198302</v>
       </c>
       <c r="D86" s="11" t="n">
         <v>11</v>
@@ -2872,10 +2872,10 @@
         <v>34</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H86" s="11" t="n">
         <v>0</v>
@@ -2887,20 +2887,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>871.8737591103564</v>
+        <v>553.3836582800872</v>
       </c>
       <c r="D87" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G87" s="11" t="n">
         <v>0</v>
@@ -2915,20 +2915,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>556.3774182767152</v>
+        <v>2895.745604122772</v>
       </c>
       <c r="D88" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G88" s="11" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>2872.029718695297</v>
+        <v>2589.178178664463</v>
       </c>
       <c r="D89" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G89" s="11" t="n">
         <v>0</v>
@@ -2971,11 +2971,11 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>2613.572568166611</v>
+        <v>1741.659648904122</v>
       </c>
       <c r="D90" s="11" t="n">
         <v>11</v>
@@ -2984,7 +2984,7 @@
         <v>21</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G90" s="11" t="n">
         <v>0</v>
@@ -2999,20 +2999,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>1756.805907806176</v>
+        <v>315.0963390442594</v>
       </c>
       <c r="D91" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G91" s="11" t="n">
         <v>0</v>
@@ -3027,23 +3027,23 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>314.2381241379629</v>
+        <v>383.2650269721146</v>
       </c>
       <c r="D92" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92" s="11" t="n">
         <v>0</v>
@@ -3055,23 +3055,23 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>378.7722323021641</v>
+        <v>157.7554582572829</v>
       </c>
       <c r="D93" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G93" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" s="11" t="n">
         <v>0</v>
@@ -3083,20 +3083,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>159.881705475761</v>
+        <v>3665.398549062854</v>
       </c>
       <c r="D94" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G94" s="11" t="n">
         <v>0</v>
@@ -3111,20 +3111,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>3703.984222982135</v>
+        <v>8783.531764204261</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G95" s="11" t="n">
         <v>0</v>
@@ -3139,20 +3139,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>8631.711784575</v>
+        <v>641.82779771</v>
       </c>
       <c r="D96" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>0</v>
@@ -3167,20 +3167,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>652.846464430693</v>
+        <v>962.7495291513903</v>
       </c>
       <c r="D97" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G97" s="11" t="n">
         <v>0</v>
@@ -3195,26 +3195,26 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>972.8830703509864</v>
+        <v>1034.4870772212</v>
       </c>
       <c r="D98" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -3223,23 +3223,23 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>1024.110311641273</v>
+        <v>1099.217023751594</v>
       </c>
       <c r="D99" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H99" s="11" t="n">
         <v>2</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>1107.408450097416</v>
+        <v>490.9999911238968</v>
       </c>
       <c r="D100" s="11" t="n">
         <v>10</v>
@@ -3264,7 +3264,7 @@
         <v>38</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G100" s="11" t="n">
         <v>0</v>
@@ -3279,26 +3279,26 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>495.8685788761032</v>
+        <v>501.0201134472656</v>
       </c>
       <c r="D101" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G101" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3307,17 +3307,17 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>504.6930349145508</v>
+        <v>1520.1945</v>
       </c>
       <c r="D102" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F102" s="11" t="n">
         <v>8</v>
@@ -3326,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -3335,11 +3335,11 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>1519.22375</v>
+        <v>897.3955894592285</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>10</v>
@@ -3348,13 +3348,13 @@
         <v>36</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G103" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>879.9082011938476</v>
+        <v>720.5413749656476</v>
       </c>
       <c r="D104" s="11" t="n">
         <v>10</v>
@@ -3376,7 +3376,7 @@
         <v>36</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G104" s="11" t="n">
         <v>0</v>
@@ -3391,11 +3391,11 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>722.1592718621234</v>
+        <v>222.2914421103889</v>
       </c>
       <c r="D105" s="11" t="n">
         <v>10</v>
@@ -3404,7 +3404,7 @@
         <v>36</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G105" s="11" t="n">
         <v>0</v>

--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026. 10. 20</t>
+          <t>2026. 10. 21</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>28308.68128640267</v>
+        <v>28328.09586081907</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>32</v>
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>39616.77175388506</v>
+        <v>39494.24844040623</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>27</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>5</v>
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>42092.98880558862</v>
+        <v>41615.40999972927</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>26</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>10</v>
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>41601.34676900319</v>
+        <v>41141.50002502802</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>26</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2200.933076956395</v>
+        <v>2232.069836527441</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>22</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>52420.72141571045</v>
+        <v>52271.01119476318</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>20</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>934.8876798875195</v>
+        <v>920.7760577437598</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>20</v>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>2838.051099853516</v>
+        <v>2783.490390014648</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>20</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>2335.595437098023</v>
+        <v>2328.120600258581</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>20</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>465.616125</v>
+        <v>469.2208858325958</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>20</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>9417.356545948278</v>
+        <v>9349.919823959139</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>20</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>184.6330990637177</v>
+        <v>187.4595433370776</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>1502.821809510193</v>
+        <v>1546.037165387879</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>19</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>10238.24892161437</v>
+        <v>10138.34405863631</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>18</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1428.975041951403</v>
+        <v>1408.14099728459</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>18</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>7564.240061649077</v>
+        <v>7632.763414017905</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>18</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>838.5614921868186</v>
+        <v>830.4977720879197</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>18</v>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>5399.725484029615</v>
+        <v>5434.94072003927</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>18</v>
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1674.333081449292</v>
+        <v>1692.1394695075</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>9</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>2130.738734050154</v>
+        <v>2160.665614118827</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>17</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>17971.12797583497</v>
+        <v>17686.0619670625</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>16</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>337.0991652513536</v>
+        <v>342.6696967136465</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>16</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2435.57076919723</v>
+        <v>2360.917610557216</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>16</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>4995.287011810465</v>
+        <v>5108.382410194185</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>16</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>780.9429728699999</v>
+        <v>800.7807114340005</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>16</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>311.212410148497</v>
+        <v>318.970598156012</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>16</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>1530.329779133544</v>
+        <v>1547.35780644</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>15</v>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>652.8778904062561</v>
+        <v>1167.596328612559</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>15</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>12</v>
@@ -1403,23 +1403,23 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>1142.817542616976</v>
+        <v>515.9549540356903</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>15</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" s="11" t="n">
         <v>0</v>
@@ -1431,23 +1431,23 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>512.9272170357361</v>
+        <v>15961.58594651311</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>0</v>
@@ -1459,23 +1459,23 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>15972.08799048795</v>
+        <v>6285.54657189822</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" s="11" t="n">
         <v>0</v>
@@ -1487,20 +1487,20 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>6348.292693211174</v>
+        <v>3975.510588295786</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G37" s="11" t="n">
         <v>2</v>
@@ -1515,11 +1515,11 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>3928.522227972212</v>
+        <v>2860.210265103084</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>14</v>
@@ -1528,10 +1528,10 @@
         <v>56</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>0</v>
@@ -1543,23 +1543,23 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>2908.511800149322</v>
+        <v>2285.212970502817</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H39" s="11" t="n">
         <v>0</v>
@@ -1571,20 +1571,20 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>2307.410455026478</v>
+        <v>513.2622038269043</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>0</v>
@@ -1599,17 +1599,17 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>503.0629936218262</v>
+        <v>915.3007902108304</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>12</v>
@@ -1627,26 +1627,26 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>904.0804225119031</v>
+        <v>741.7747800599315</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1655,26 +1655,26 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>728.5659143625229</v>
+        <v>1211.8244246275</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F43" s="11" t="n">
         <v>4</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1683,20 +1683,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>1185.349741892308</v>
+        <v>660.5588444869852</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G44" s="11" t="n">
         <v>0</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>3652.133957301473</v>
+        <v>3763.256243187947</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>14</v>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>852.8466701664112</v>
+        <v>855.3162527328222</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>14</v>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>726.0911501775</v>
+        <v>676.4273608236649</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>14</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>4019.441424028571</v>
+        <v>4022.453195368332</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>14</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>497.173587748081</v>
+        <v>494.0855550146192</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>14</v>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1549.138964266283</v>
+        <v>1571.793219899572</v>
       </c>
       <c r="D50" s="11" t="n">
         <v>14</v>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>1512.926277811893</v>
+        <v>1505.417786742071</v>
       </c>
       <c r="D51" s="11" t="n">
         <v>13</v>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>1995.363474884033</v>
+        <v>1995.19883972168</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>12</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1259.952384230827</v>
+        <v>1231.662901841812</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>12</v>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>2419.480789738685</v>
+        <v>2371.247817233293</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>12</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1910.883940803029</v>
+        <v>1923.967119631442</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>12</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>1892.276112668637</v>
+        <v>1928.191231846818</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>12</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1272.247138958054</v>
+        <v>1304.436707246108</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>12</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>11060.62505038597</v>
+        <v>11446.92803705403</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>12</v>
@@ -2103,11 +2103,11 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>50049.28124830322</v>
+        <v>397.283740367395</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>12</v>
@@ -2116,13 +2116,13 @@
         <v>38</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H59" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2131,26 +2131,26 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>395.1336966608825</v>
+        <v>49547.2411</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H60" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>867.794179718005</v>
+        <v>882.9886920819558</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>12</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>355.6493893790611</v>
+        <v>363.8514937264072</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>12</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1261.242800415039</v>
+        <v>1291.577745605469</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>12</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>312.1632823984335</v>
+        <v>308.7110251215665</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>12</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>1897.999446575528</v>
+        <v>1940.653744977729</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>12</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>298.4839444397049</v>
+        <v>299.465156072049</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>12</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>3523.645858443151</v>
+        <v>3541.127729355651</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>12</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>580.4567182869519</v>
+        <v>599.1420928148798</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>12</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>627.8540033123382</v>
+        <v>627.5323698686691</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>12</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>274.7663912228318</v>
+        <v>279.848491546556</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>12</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>4401.24917009239</v>
+        <v>4427.534881444839</v>
       </c>
       <c r="D71" s="11" t="n">
         <v>12</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>932.5015994401825</v>
+        <v>917.0892068284762</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>12</v>
@@ -2480,13 +2480,13 @@
         <v>27</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G72" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>147.4650419468829</v>
+        <v>154.4596973447626</v>
       </c>
       <c r="D73" s="11" t="n">
         <v>12</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>186.2958081920508</v>
+        <v>207.4078275106201</v>
       </c>
       <c r="D74" s="11" t="n">
         <v>12</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>1682.607663303897</v>
+        <v>1715.537856982867</v>
       </c>
       <c r="D75" s="11" t="n">
         <v>12</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>1001.6222222925</v>
+        <v>988.9853075314993</v>
       </c>
       <c r="D76" s="11" t="n">
         <v>12</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>788.75785071</v>
+        <v>810.1613462039594</v>
       </c>
       <c r="D77" s="11" t="n">
         <v>12</v>
@@ -2639,13 +2639,13 @@
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>233.5782392514702</v>
+        <v>233.260750576766</v>
       </c>
       <c r="D78" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F78" s="11" t="n">
         <v>8</v>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>422.6629206554684</v>
+        <v>433.821619595442</v>
       </c>
       <c r="D79" s="11" t="n">
         <v>12</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>2136.747867325885</v>
+        <v>2149.781297641615</v>
       </c>
       <c r="D80" s="11" t="n">
         <v>12</v>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>520.9668936453644</v>
+        <v>529.9105657146356</v>
       </c>
       <c r="D81" s="11" t="n">
         <v>12</v>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>744.4797001375432</v>
+        <v>753.6471998349353</v>
       </c>
       <c r="D82" s="11" t="n">
         <v>12</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>171.3539231212747</v>
+        <v>174.8615602014047</v>
       </c>
       <c r="D83" s="11" t="n">
         <v>12</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>568.7761878375586</v>
+        <v>566.8160578390845</v>
       </c>
       <c r="D84" s="11" t="n">
         <v>11</v>
@@ -2831,23 +2831,23 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>2320.758543861598</v>
+        <v>214.534557027339</v>
       </c>
       <c r="D85" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F85" s="11" t="n">
         <v>10</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H85" s="11" t="n">
         <v>0</v>
@@ -2859,11 +2859,11 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>860.865233198302</v>
+        <v>2313.613407607091</v>
       </c>
       <c r="D86" s="11" t="n">
         <v>11</v>
@@ -2872,10 +2872,10 @@
         <v>34</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H86" s="11" t="n">
         <v>0</v>
@@ -2887,20 +2887,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>553.3836582800872</v>
+        <v>860.2537054544654</v>
       </c>
       <c r="D87" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G87" s="11" t="n">
         <v>0</v>
@@ -2915,20 +2915,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>2895.745604122772</v>
+        <v>566.9554683953488</v>
       </c>
       <c r="D88" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G88" s="11" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>2589.178178664463</v>
+        <v>2934.657313377228</v>
       </c>
       <c r="D89" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G89" s="11" t="n">
         <v>0</v>
@@ -2975,16 +2975,16 @@
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>1741.659648904122</v>
+        <v>1747.978435662931</v>
       </c>
       <c r="D90" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" s="11" t="n">
         <v>0</v>
@@ -2999,20 +2999,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>315.0963390442594</v>
+        <v>2605.755546253223</v>
       </c>
       <c r="D91" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G91" s="11" t="n">
         <v>0</v>
@@ -3027,23 +3027,23 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>383.2650269721146</v>
+        <v>317.2192699424075</v>
       </c>
       <c r="D92" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H92" s="11" t="n">
         <v>0</v>
@@ -3055,23 +3055,23 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>157.7554582572829</v>
+        <v>384.4969387814922</v>
       </c>
       <c r="D93" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G93" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H93" s="11" t="n">
         <v>0</v>
@@ -3083,20 +3083,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>3665.398549062854</v>
+        <v>159.46827102</v>
       </c>
       <c r="D94" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G94" s="11" t="n">
         <v>0</v>
@@ -3111,20 +3111,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>8783.531764204261</v>
+        <v>3700.481697596001</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G95" s="11" t="n">
         <v>0</v>
@@ -3139,20 +3139,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>641.82779771</v>
+        <v>8729.496880169409</v>
       </c>
       <c r="D96" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>0</v>
@@ -3167,20 +3167,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>962.7495291513903</v>
+        <v>650.3978592461139</v>
       </c>
       <c r="D97" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G97" s="11" t="n">
         <v>0</v>
@@ -3195,26 +3195,26 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>1034.4870772212</v>
+        <v>974.3236986473767</v>
       </c>
       <c r="D98" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -3223,23 +3223,23 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>1099.217023751594</v>
+        <v>1043.212920124982</v>
       </c>
       <c r="D99" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H99" s="11" t="n">
         <v>2</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>490.9999911238968</v>
+        <v>1113.171681652732</v>
       </c>
       <c r="D100" s="11" t="n">
         <v>10</v>
@@ -3264,7 +3264,7 @@
         <v>38</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G100" s="11" t="n">
         <v>0</v>
@@ -3279,26 +3279,26 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>501.0201134472656</v>
+        <v>504.355654601471</v>
       </c>
       <c r="D101" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G101" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -3307,17 +3307,17 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>1520.1945</v>
+        <v>511.0959003442383</v>
       </c>
       <c r="D102" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F102" s="11" t="n">
         <v>8</v>
@@ -3326,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3335,11 +3335,11 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>897.3955894592285</v>
+        <v>1483.610362670898</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>10</v>
@@ -3348,13 +3348,13 @@
         <v>36</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G103" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>720.5413749656476</v>
+        <v>880.8995756530762</v>
       </c>
       <c r="D104" s="11" t="n">
         <v>10</v>
@@ -3376,7 +3376,7 @@
         <v>36</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G104" s="11" t="n">
         <v>0</v>
@@ -3391,11 +3391,11 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>222.2914421103889</v>
+        <v>728.2264778021234</v>
       </c>
       <c r="D105" s="11" t="n">
         <v>10</v>
@@ -3404,7 +3404,7 @@
         <v>36</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G105" s="11" t="n">
         <v>0</v>

--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026. 10. 21</t>
+          <t>2026. 10. 22</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>28328.09586081907</v>
+        <v>28300.05039218093</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>32</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>39494.24844040623</v>
+        <v>39574.44560072316</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>27</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>41615.40999972927</v>
+        <v>40940.93103458518</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>26</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>41141.50002502802</v>
+        <v>40474.97081610646</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>26</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2232.069836527441</v>
+        <v>2242.491620956335</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>22</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>52271.01119476318</v>
+        <v>53599.09619476318</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>20</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>920.7760577437598</v>
+        <v>980.5979698918799</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>20</v>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>2783.490390014648</v>
+        <v>2840.505</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>20</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>2328.120600258581</v>
+        <v>2450.685613345186</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>20</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>469.2208858325958</v>
+        <v>469.8817639995575</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>20</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>9349.919823959139</v>
+        <v>9345.95331401672</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>20</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>187.4595433370776</v>
+        <v>187.8786912529224</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>1546.037165387879</v>
+        <v>1583.049443918457</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>19</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>10138.34405863631</v>
+        <v>10337.47426772194</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>18</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1408.14099728459</v>
+        <v>1381.179209920789</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>18</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>7632.763414017905</v>
+        <v>7656.793538416172</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>18</v>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>830.4977720879197</v>
+        <v>5454.213045654077</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>18</v>
@@ -1080,7 +1080,7 @@
         <v>54</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>0</v>
@@ -1095,20 +1095,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>5434.94072003927</v>
+        <v>799.213820579866</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G23" s="11" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1692.1394695075</v>
+        <v>1649.2326049875</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>18</v>
@@ -1151,23 +1151,23 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>2160.665614118827</v>
+        <v>17769.36591817981</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>17</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" s="11" t="n">
         <v>0</v>
@@ -1179,23 +1179,23 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>17686.0619670625</v>
+        <v>2199.669361411482</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="11" t="n">
         <v>0</v>
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>342.6696967136465</v>
+        <v>340.9599256732438</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>16</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>15</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2360.917610557216</v>
+        <v>2419.977918385824</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>16</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>5108.382410194185</v>
+        <v>5032.749811967441</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>16</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>800.7807114340005</v>
+        <v>806.7051392729981</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>16</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>318.970598156012</v>
+        <v>327.0618377483383</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>16</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>1547.35780644</v>
+        <v>1512.453919035696</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>15</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>1167.596328612559</v>
+        <v>1141.513408307441</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>15</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>515.9549540356903</v>
+        <v>518.9987989107361</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>15</v>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>15961.58594651311</v>
+        <v>16125.32110125151</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>14</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>6285.54657189822</v>
+        <v>6462.260512509092</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>14</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>3975.510588295786</v>
+        <v>3914.577581726217</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>14</v>
@@ -1515,23 +1515,23 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>2860.210265103084</v>
+        <v>2324.815416752113</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>0</v>
@@ -1543,20 +1543,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>2285.212970502817</v>
+        <v>511.7155923461914</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G39" s="11" t="n">
         <v>0</v>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>513.2622038269043</v>
+        <v>899.9819562548788</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>12</v>
@@ -1599,26 +1599,26 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>915.3007902108304</v>
+        <v>758.3971683947714</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1627,26 +1627,26 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>741.7747800599315</v>
+        <v>1195.197770799422</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>4</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1655,20 +1655,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>1211.8244246275</v>
+        <v>645.0520376977636</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G43" s="11" t="n">
         <v>0</v>
@@ -1683,20 +1683,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>660.5588444869852</v>
+        <v>827.7314264232056</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G44" s="11" t="n">
         <v>0</v>
@@ -1711,17 +1711,17 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>3763.256243187947</v>
+        <v>667.8283732106391</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>8</v>
@@ -1739,26 +1739,26 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>855.3162527328222</v>
+        <v>3987.602651542738</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G46" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1767,20 +1767,20 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>676.4273608236649</v>
+        <v>503.2108884269238</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0</v>
@@ -1795,17 +1795,17 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>4022.453195368332</v>
+        <v>1584.763237754572</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F48" s="11" t="n">
         <v>8</v>
@@ -1823,23 +1823,23 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>494.0855550146192</v>
+        <v>2708.226403392406</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H49" s="11" t="n">
         <v>0</v>
@@ -1851,17 +1851,17 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1571.793219899572</v>
+        <v>1519.723464807928</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F50" s="11" t="n">
         <v>8</v>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1879,20 +1879,20 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>1505.417786742071</v>
+        <v>3742.97051199</v>
       </c>
       <c r="D51" s="11" t="n">
         <v>13</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G51" s="11" t="n">
         <v>0</v>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>1995.19883972168</v>
+        <v>1989.849389953613</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>12</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1231.662901841812</v>
+        <v>1190.036472588501</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>12</v>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>2371.247817233293</v>
+        <v>2466.035847679207</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>12</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1923.967119631442</v>
+        <v>1967.14192030826</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>12</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>1928.191231846818</v>
+        <v>1930.953994123181</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>12</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1304.436707246108</v>
+        <v>1329.453288068887</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>12</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>11446.92803705403</v>
+        <v>11331.803916745</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>12</v>
@@ -2103,11 +2103,11 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>397.283740367395</v>
+        <v>916.4345636126812</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>12</v>
@@ -2131,26 +2131,26 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>49547.2411</v>
+        <v>409.5543854478149</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H60" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2159,11 +2159,11 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>882.9886920819558</v>
+        <v>50202.51835678711</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>12</v>
@@ -2172,13 +2172,13 @@
         <v>37</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>363.8514937264072</v>
+        <v>367.0785549584389</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>12</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1291.577745605469</v>
+        <v>1306.435690795898</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>12</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>308.7110251215665</v>
+        <v>301.2043327850604</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>12</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>1940.653744977729</v>
+        <v>1904.199222350528</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>12</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>299.465156072049</v>
+        <v>294.9053681794098</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>12</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>3541.127729355651</v>
+        <v>3550.917534386303</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>12</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>599.1420928148798</v>
+        <v>611.145093645488</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>12</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>627.5323698686691</v>
+        <v>633.8581111638309</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>12</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>279.848491546556</v>
+        <v>283.1810257271166</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>12</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>4427.534881444839</v>
+        <v>4448.523880831847</v>
       </c>
       <c r="D71" s="11" t="n">
         <v>12</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>917.0892068284762</v>
+        <v>959.2517633042701</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>12</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>154.4596973447626</v>
+        <v>153.8822687816455</v>
       </c>
       <c r="D73" s="11" t="n">
         <v>12</v>
@@ -2523,20 +2523,20 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>207.4078275106201</v>
+        <v>1687.50761015299</v>
       </c>
       <c r="D74" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G74" s="11" t="n">
         <v>0</v>
@@ -2551,11 +2551,11 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>1715.537856982867</v>
+        <v>989.4160952588885</v>
       </c>
       <c r="D75" s="11" t="n">
         <v>12</v>
@@ -2567,7 +2567,7 @@
         <v>8</v>
       </c>
       <c r="G75" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H75" s="11" t="n">
         <v>0</v>
@@ -2579,11 +2579,11 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>988.9853075314993</v>
+        <v>804.2687543358326</v>
       </c>
       <c r="D76" s="11" t="n">
         <v>12</v>
@@ -2592,10 +2592,10 @@
         <v>24</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G76" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H76" s="11" t="n">
         <v>0</v>
@@ -2607,26 +2607,26 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>TPR</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>810.1613462039594</v>
+        <v>228.5181471141193</v>
       </c>
       <c r="D77" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G77" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -2635,26 +2635,26 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>233.260750576766</v>
+        <v>426.1185161519525</v>
       </c>
       <c r="D78" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2663,26 +2663,26 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>433.821619595442</v>
+        <v>537.2890653191721</v>
       </c>
       <c r="D79" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G79" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2691,20 +2691,20 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>2149.781297641615</v>
+        <v>744.559434449892</v>
       </c>
       <c r="D80" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G80" s="11" t="n">
         <v>0</v>
@@ -2719,23 +2719,23 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>529.9105657146356</v>
+        <v>176.1662087285779</v>
       </c>
       <c r="D81" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G81" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H81" s="11" t="n">
         <v>2</v>
@@ -2747,20 +2747,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>753.6471998349353</v>
+        <v>562.6437475563379</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G82" s="11" t="n">
         <v>0</v>
@@ -2775,26 +2775,26 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>174.8615602014047</v>
+        <v>214.904971567661</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G83" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H83" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2803,23 +2803,23 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>566.8160578390845</v>
+        <v>2307.528435692296</v>
       </c>
       <c r="D84" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F84" s="11" t="n">
         <v>10</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H84" s="11" t="n">
         <v>0</v>
@@ -2831,20 +2831,20 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>214.534557027339</v>
+        <v>890.4659569441089</v>
       </c>
       <c r="D85" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G85" s="11" t="n">
         <v>0</v>
@@ -2859,23 +2859,23 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>2313.613407607091</v>
+        <v>572.3442566921511</v>
       </c>
       <c r="D86" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H86" s="11" t="n">
         <v>0</v>
@@ -2887,20 +2887,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>860.2537054544654</v>
+        <v>3089.287020745544</v>
       </c>
       <c r="D87" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G87" s="11" t="n">
         <v>0</v>
@@ -2915,20 +2915,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>566.9554683953488</v>
+        <v>206.2682405120508</v>
       </c>
       <c r="D88" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G88" s="11" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>2934.657313377228</v>
+        <v>1780.376963654122</v>
       </c>
       <c r="D89" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G89" s="11" t="n">
         <v>0</v>
@@ -2971,20 +2971,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>1747.978435662931</v>
+        <v>2582.304686164629</v>
       </c>
       <c r="D90" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G90" s="11" t="n">
         <v>0</v>
@@ -2999,20 +2999,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>2605.755546253223</v>
+        <v>311.7086921542593</v>
       </c>
       <c r="D91" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G91" s="11" t="n">
         <v>0</v>
@@ -3027,20 +3027,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>317.2192699424075</v>
+        <v>2185.370051648961</v>
       </c>
       <c r="D92" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G92" s="11" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>384.4969387814922</v>
+        <v>375.5838018336563</v>
       </c>
       <c r="D93" s="11" t="n">
         <v>11</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>159.46827102</v>
+        <v>158.3460837363317</v>
       </c>
       <c r="D94" s="11" t="n">
         <v>11</v>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>3700.481697596001</v>
+        <v>3642.879169081999</v>
       </c>
       <c r="D95" s="11" t="n">
         <v>11</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>8729.496880169409</v>
+        <v>9023.015573878227</v>
       </c>
       <c r="D96" s="11" t="n">
         <v>10</v>
@@ -3171,13 +3171,13 @@
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>650.3978592461139</v>
+        <v>654.1078465161139</v>
       </c>
       <c r="D97" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F97" s="11" t="n">
         <v>10</v>
@@ -3199,13 +3199,13 @@
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>974.3236986473767</v>
+        <v>981.7832757</v>
       </c>
       <c r="D98" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F98" s="11" t="n">
         <v>12</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>1043.212920124982</v>
+        <v>1024.051385459982</v>
       </c>
       <c r="D99" s="11" t="n">
         <v>10</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>1113.171681652732</v>
+        <v>1102.125746100463</v>
       </c>
       <c r="D100" s="11" t="n">
         <v>10</v>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>504.355654601471</v>
+        <v>511.0005334992645</v>
       </c>
       <c r="D101" s="11" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>511.0959003442383</v>
+        <v>510.5395586206055</v>
       </c>
       <c r="D102" s="11" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>1483.610362670898</v>
+        <v>1530.062969482422</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>10</v>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>880.8995756530762</v>
+        <v>897.9739752703857</v>
       </c>
       <c r="D104" s="11" t="n">
         <v>10</v>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>728.2264778021234</v>
+        <v>721.5930017764758</v>
       </c>
       <c r="D105" s="11" t="n">
         <v>10</v>

--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026. 10. 22</t>
+          <t>2026. 10. 23</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>28300.05039218093</v>
+        <v>27006.77244824907</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>32</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>39574.44560072316</v>
+        <v>38693.03371351692</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>27</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>40940.93103458518</v>
+        <v>39651.8948583594</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>26</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>40474.97081610646</v>
+        <v>39228.74015824518</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>26</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2242.491620956335</v>
+        <v>2171.983588508895</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>22</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>53599.09619476318</v>
+        <v>51242.35032119751</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>20</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>980.5979698918799</v>
+        <v>925.51587436</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>20</v>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>2840.505</v>
+        <v>2903.245709838867</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>20</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>2450.685613345186</v>
+        <v>2436.350588053209</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>20</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>469.8817639995575</v>
+        <v>474.7481888317108</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>20</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>9345.95331401672</v>
+        <v>9609.353665006049</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>20</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>187.8786912529224</v>
+        <v>184.04201195</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>1583.049443918457</v>
+        <v>1623.16334</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>19</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>10337.47426772194</v>
+        <v>9690.526557968253</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>18</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1381.179209920789</v>
+        <v>1410.796269341301</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>18</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>7656.793538416172</v>
+        <v>7778.633711389797</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>18</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>5454.213045654077</v>
+        <v>5546.982733556652</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>18</v>
@@ -1080,13 +1080,13 @@
         <v>54</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>799.213820579866</v>
+        <v>805.6699496261072</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>18</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1649.2326049875</v>
+        <v>1703.295182264952</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>18</v>
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>17769.36591817981</v>
+        <v>16529.49351896274</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>17</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>13</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>2199.669361411482</v>
+        <v>2008.335209641615</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>17</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>340.9599256732438</v>
+        <v>306.6543422962193</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>16</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2419.977918385824</v>
+        <v>2243.86505865446</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>16</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>5032.749811967441</v>
+        <v>5039.641828234012</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>16</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>806.7051392729981</v>
+        <v>835.6089480985025</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>16</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>327.0618377483383</v>
+        <v>336.8103275483383</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>16</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>1512.453919035696</v>
+        <v>1568.02459322538</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>15</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>1141.513408307441</v>
+        <v>1177.87605815163</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>15</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>518.9987989107361</v>
+        <v>522.2369759107361</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>15</v>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>16125.32110125151</v>
+        <v>15430.28070945121</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>14</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>6462.260512509092</v>
+        <v>6014.598181560606</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>14</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>3914.577581726217</v>
+        <v>3805.746570208822</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>14</v>
@@ -1515,23 +1515,23 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>2324.815416752113</v>
+        <v>2791.921679831355</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>0</v>
@@ -1543,20 +1543,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>511.7155923461914</v>
+        <v>2157.577097708452</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G39" s="11" t="n">
         <v>0</v>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>899.9819562548788</v>
+        <v>532.8454936218262</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>12</v>
@@ -1599,26 +1599,26 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>758.3971683947714</v>
+        <v>887.8209619979758</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1627,26 +1627,26 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>1195.197770799422</v>
+        <v>735.3929596373857</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>4</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1655,20 +1655,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>645.0520376977636</v>
+        <v>1208.371247565386</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G43" s="11" t="n">
         <v>0</v>
@@ -1683,20 +1683,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>827.7314264232056</v>
+        <v>666.7904805877636</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G44" s="11" t="n">
         <v>0</v>
@@ -1711,20 +1711,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>667.8283732106391</v>
+        <v>846.0436932815333</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G45" s="11" t="n">
         <v>0</v>
@@ -1739,17 +1739,17 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>3987.602651542738</v>
+        <v>677.4803267727912</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F46" s="11" t="n">
         <v>8</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1767,26 +1767,26 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>503.2108884269238</v>
+        <v>4102.050290712141</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1795,26 +1795,26 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1584.763237754572</v>
+        <v>447.2793078392285</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1823,26 +1823,26 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>2708.226403392406</v>
+        <v>1581.30461910171</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1519.723464807928</v>
+        <v>1482.338996630179</v>
       </c>
       <c r="D50" s="11" t="n">
         <v>13</v>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>3742.97051199</v>
+        <v>3814.598679393315</v>
       </c>
       <c r="D51" s="11" t="n">
         <v>13</v>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>1989.849389953613</v>
+        <v>2059.886644744873</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>12</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1190.036472588501</v>
+        <v>1210.474031360626</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>12</v>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>2466.035847679207</v>
+        <v>2203.697270394207</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>12</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1967.14192030826</v>
+        <v>1869.259785104846</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>12</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>1930.953994123181</v>
+        <v>1953.400844807728</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>12</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1329.453288068887</v>
+        <v>1356.446783654724</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>12</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>11331.803916745</v>
+        <v>11652.29525555667</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>12</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>916.4345636126812</v>
+        <v>868.3336757260881</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>12</v>
@@ -2119,10 +2119,10 @@
         <v>7</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>409.5543854478149</v>
+        <v>389.5128379847901</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>12</v>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>50202.51835678711</v>
+        <v>50819.85377415161</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>12</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>367.0785549584389</v>
+        <v>364.1204219073439</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>12</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1306.435690795898</v>
+        <v>1335.738817993164</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>12</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>301.2043327850604</v>
+        <v>304.1213617569879</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>12</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>1904.199222350528</v>
+        <v>1949.085538416843</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>12</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>294.9053681794098</v>
+        <v>289.0949853573441</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>12</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>3550.917534386303</v>
+        <v>3571.895992883047</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>12</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>611.145093645488</v>
+        <v>599.6211724246323</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>12</v>
@@ -2383,26 +2383,26 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>633.8581111638309</v>
+        <v>276.5159573659955</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G69" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -2411,11 +2411,11 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>283.1810257271166</v>
+        <v>620.8635965263633</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>12</v>
@@ -2424,13 +2424,13 @@
         <v>30</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G70" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>4448.523880831847</v>
+        <v>4446.562157831086</v>
       </c>
       <c r="D71" s="11" t="n">
         <v>12</v>
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>959.2517633042701</v>
+        <v>904.2278857336269</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F72" s="11" t="n">
         <v>7</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>153.8822687816455</v>
+        <v>160.7172043120569</v>
       </c>
       <c r="D73" s="11" t="n">
         <v>12</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>1687.50761015299</v>
+        <v>1710.637910133775</v>
       </c>
       <c r="D74" s="11" t="n">
         <v>12</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>989.4160952588885</v>
+        <v>927.5236655171676</v>
       </c>
       <c r="D75" s="11" t="n">
         <v>12</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>804.2687543358326</v>
+        <v>834.6828600791674</v>
       </c>
       <c r="D76" s="11" t="n">
         <v>12</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>228.5181471141193</v>
+        <v>226.0575379729404</v>
       </c>
       <c r="D77" s="11" t="n">
         <v>12</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>426.1185161519525</v>
+        <v>422.7349276760422</v>
       </c>
       <c r="D78" s="11" t="n">
         <v>12</v>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>537.2890653191721</v>
+        <v>577.4236423346356</v>
       </c>
       <c r="D79" s="11" t="n">
         <v>12</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>744.559434449892</v>
+        <v>776.3666132975432</v>
       </c>
       <c r="D80" s="11" t="n">
         <v>12</v>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>176.1662087285779</v>
+        <v>181.5262138007684</v>
       </c>
       <c r="D81" s="11" t="n">
         <v>12</v>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>562.6437475563379</v>
+        <v>552.0310162396948</v>
       </c>
       <c r="D82" s="11" t="n">
         <v>11</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>214.904971567661</v>
+        <v>215.2059201349195</v>
       </c>
       <c r="D83" s="11" t="n">
         <v>11</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>2307.528435692296</v>
+        <v>2352.658292360409</v>
       </c>
       <c r="D84" s="11" t="n">
         <v>11</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>890.4659569441089</v>
+        <v>863.923151878302</v>
       </c>
       <c r="D85" s="11" t="n">
         <v>11</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>572.3442566921511</v>
+        <v>575.0054048875872</v>
       </c>
       <c r="D86" s="11" t="n">
         <v>11</v>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>3089.287020745544</v>
+        <v>2879.913928738861</v>
       </c>
       <c r="D87" s="11" t="n">
         <v>11</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>206.2682405120508</v>
+        <v>219.8612336573291</v>
       </c>
       <c r="D88" s="11" t="n">
         <v>11</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>1780.376963654122</v>
+        <v>1761.312656176904</v>
       </c>
       <c r="D89" s="11" t="n">
         <v>11</v>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>2582.304686164629</v>
+        <v>2624.219972669092</v>
       </c>
       <c r="D90" s="11" t="n">
         <v>11</v>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>311.7086921542593</v>
+        <v>322.5943129077777</v>
       </c>
       <c r="D91" s="11" t="n">
         <v>11</v>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>2185.370051648961</v>
+        <v>2195.905074644911</v>
       </c>
       <c r="D92" s="11" t="n">
         <v>11</v>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>375.5838018336563</v>
+        <v>390.2940976528855</v>
       </c>
       <c r="D93" s="11" t="n">
         <v>11</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>158.3460837363317</v>
+        <v>162.5985781732878</v>
       </c>
       <c r="D94" s="11" t="n">
         <v>11</v>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>3642.879169081999</v>
+        <v>3846.112996381999</v>
       </c>
       <c r="D95" s="11" t="n">
         <v>11</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>9023.015573878227</v>
+        <v>8291.830361264558</v>
       </c>
       <c r="D96" s="11" t="n">
         <v>10</v>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>654.1078465161139</v>
+        <v>634.1852329913861</v>
       </c>
       <c r="D97" s="11" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>981.7832757</v>
+        <v>939.9662103552466</v>
       </c>
       <c r="D98" s="11" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>1024.051385459982</v>
+        <v>1036.255762296291</v>
       </c>
       <c r="D99" s="11" t="n">
         <v>10</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>1102.125746100463</v>
+        <v>1145.916952313426</v>
       </c>
       <c r="D100" s="11" t="n">
         <v>10</v>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>511.0005334992645</v>
+        <v>521.4613664425248</v>
       </c>
       <c r="D101" s="11" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>510.5395586206055</v>
+        <v>528.9703031030274</v>
       </c>
       <c r="D102" s="11" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>1530.062969482422</v>
+        <v>1433.157122070312</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>10</v>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>897.9739752703857</v>
+        <v>852.7544076913452</v>
       </c>
       <c r="D104" s="11" t="n">
         <v>10</v>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>721.5930017764758</v>
+        <v>744.24392864</v>
       </c>
       <c r="D105" s="11" t="n">
         <v>10</v>

--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026. 10. 23</t>
+          <t>2026. 10. 26</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>27006.77244824907</v>
+        <v>26750.05765856</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>32</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>38693.03371351692</v>
+        <v>38947.72937999503</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>27</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>39651.8948583594</v>
+        <v>39161.47327730672</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>26</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>39228.74015824518</v>
+        <v>38803.13708250561</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>26</v>
@@ -735,16 +735,16 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2171.983588508895</v>
+        <v>2170.310888574184</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>62</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>2</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>51242.35032119751</v>
+        <v>50940.51282119751</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>20</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>925.51587436</v>
+        <v>968.2457802997998</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>20</v>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>2903.245709838867</v>
+        <v>3112.898900146484</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>20</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>2436.350588053209</v>
+        <v>2637.349047534628</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>20</v>
@@ -875,16 +875,16 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>474.7481888317108</v>
+        <v>459.3678514995575</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>20</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>0</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>9609.353665006049</v>
+        <v>9511.768319911156</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>20</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>184.04201195</v>
+        <v>184.8372942846918</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>1623.16334</v>
+        <v>1643.427104612122</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>19</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>9690.526557968253</v>
+        <v>9928.804258792816</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>18</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1410.796269341301</v>
+        <v>1362.387538373012</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>18</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>7778.633711389797</v>
+        <v>7658.107824599078</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>18</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>5546.982733556652</v>
+        <v>5462.797771970386</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>18</v>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>805.6699496261072</v>
+        <v>777.2498605477258</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>18</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1703.295182264952</v>
+        <v>1571.892909672452</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>18</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>16529.49351896274</v>
+        <v>16370.78437870505</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>17</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>2008.335209641615</v>
+        <v>2053.629861798981</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>17</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>306.6543422962193</v>
+        <v>299.1258794610123</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>16</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2243.86505865446</v>
+        <v>2246.321409733338</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>16</v>
@@ -1248,13 +1248,13 @@
         <v>42</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G28" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>5039.641828234012</v>
+        <v>5047.594071729071</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>16</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>835.6089480985025</v>
+        <v>819.9003250810025</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>16</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>336.8103275483383</v>
+        <v>341.4977174688294</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>16</v>
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>1568.02459322538</v>
+        <v>15355.81220010091</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>15</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>1177.87605815163</v>
+        <v>1178.144587377559</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>15</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>522.2369759107361</v>
+        <v>523.0303628749847</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>15</v>
@@ -1431,23 +1431,23 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>15430.28070945121</v>
+        <v>6057.996256948257</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>0</v>
@@ -1459,20 +1459,20 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>6014.598181560606</v>
+        <v>3824.541960595288</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G36" s="11" t="n">
         <v>2</v>
@@ -1487,23 +1487,23 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>3805.746570208822</v>
+        <v>2741.954213109323</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>0</v>
@@ -1515,23 +1515,23 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>2791.921679831355</v>
+        <v>2173.972864174365</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>0</v>
@@ -1543,20 +1543,20 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>2157.577097708452</v>
+        <v>874.2826034024999</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G39" s="11" t="n">
         <v>0</v>
@@ -1571,26 +1571,26 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>532.8454936218262</v>
+        <v>783.1656202697754</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1599,26 +1599,26 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>887.8209619979758</v>
+        <v>1597.841268257532</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1627,26 +1627,26 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>735.3929596373857</v>
+        <v>1195.453619516731</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>4</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1655,20 +1655,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>1208.371247565386</v>
+        <v>662.1529505272612</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G43" s="11" t="n">
         <v>0</v>
@@ -1683,20 +1683,20 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>666.7904805877636</v>
+        <v>880.5247083935889</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G44" s="11" t="n">
         <v>0</v>
@@ -1711,20 +1711,20 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>846.0436932815333</v>
+        <v>644.5607844543457</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G45" s="11" t="n">
         <v>0</v>
@@ -1739,17 +1739,17 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>677.4803267727912</v>
+        <v>3988.893363794285</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F46" s="11" t="n">
         <v>8</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1767,26 +1767,26 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>4102.050290712141</v>
+        <v>446.1342997996143</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1795,26 +1795,26 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>447.2793078392285</v>
+        <v>1566.432321406283</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1823,26 +1823,26 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>1581.30461910171</v>
+        <v>527.0979936218262</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G49" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1482.338996630179</v>
+        <v>1488.661980910358</v>
       </c>
       <c r="D50" s="11" t="n">
         <v>13</v>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>3814.598679393315</v>
+        <v>3752.754262951395</v>
       </c>
       <c r="D51" s="11" t="n">
         <v>13</v>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>2059.886644744873</v>
+        <v>2045.73116027832</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>12</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1210.474031360626</v>
+        <v>1207.493081007248</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>12</v>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>2203.697270394207</v>
+        <v>2170.61868515</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>12</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1869.259785104846</v>
+        <v>1894.990199466135</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>12</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>1953.400844807728</v>
+        <v>1942.868044166667</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>12</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1356.446783654724</v>
+        <v>1327.957800549168</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>12</v>
@@ -2060,13 +2060,13 @@
         <v>40</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G57" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H57" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>11652.29525555667</v>
+        <v>11355.96976051111</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>12</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>868.3336757260881</v>
+        <v>854.7575141973188</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>12</v>
@@ -2119,10 +2119,10 @@
         <v>7</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>389.5128379847901</v>
+        <v>402.0445815608826</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>12</v>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>50819.85377415161</v>
+        <v>50748.3437173645</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>12</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>364.1204219073439</v>
+        <v>351.0777128887489</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>12</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1335.738817993164</v>
+        <v>1327.513872802734</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>12</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>304.1213617569879</v>
+        <v>299.7725654219879</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>12</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>1949.085538416843</v>
+        <v>1934.825940613058</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>12</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>289.0949853573441</v>
+        <v>277.531965675</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>12</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>3571.895992883047</v>
+        <v>3500.114850377553</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>12</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>599.6211724246323</v>
+        <v>592.3840729435361</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>12</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>276.5159573659955</v>
+        <v>288.8325034812643</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>12</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>620.8635965263633</v>
+        <v>648.3750677274353</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>12</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>4446.562157831086</v>
+        <v>4574.655126994839</v>
       </c>
       <c r="D71" s="11" t="n">
         <v>12</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>904.2278857336269</v>
+        <v>897.9920412628969</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>12</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>160.7172043120569</v>
+        <v>159.7712077824683</v>
       </c>
       <c r="D73" s="11" t="n">
         <v>12</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>1710.637910133775</v>
+        <v>1710.06154928147</v>
       </c>
       <c r="D74" s="11" t="n">
         <v>12</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>927.5236655171676</v>
+        <v>935.9962258737778</v>
       </c>
       <c r="D75" s="11" t="n">
         <v>12</v>
@@ -2579,26 +2579,26 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>TPR</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>834.6828600791674</v>
+        <v>219.0130924155895</v>
       </c>
       <c r="D76" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G76" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -2607,26 +2607,26 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>226.0575379729404</v>
+        <v>416.1836893980475</v>
       </c>
       <c r="D77" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G77" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H77" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2635,26 +2635,26 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>422.7349276760422</v>
+        <v>573.2871790762915</v>
       </c>
       <c r="D78" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H78" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2663,26 +2663,26 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>577.4236423346356</v>
+        <v>749.6613356899353</v>
       </c>
       <c r="D79" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G79" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2691,26 +2691,26 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>776.3666132975432</v>
+        <v>178.8725544287253</v>
       </c>
       <c r="D80" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H80" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2719,26 +2719,26 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>181.5262138007684</v>
+        <v>942.3442317135205</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G81" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H81" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>552.0310162396948</v>
+        <v>576.14072204</v>
       </c>
       <c r="D82" s="11" t="n">
         <v>11</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>215.2059201349195</v>
+        <v>223.0330639534536</v>
       </c>
       <c r="D83" s="11" t="n">
         <v>11</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>2352.658292360409</v>
+        <v>2345.605301493708</v>
       </c>
       <c r="D84" s="11" t="n">
         <v>11</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>863.923151878302</v>
+        <v>877.0110400958911</v>
       </c>
       <c r="D85" s="11" t="n">
         <v>11</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>575.0054048875872</v>
+        <v>564.7600173273256</v>
       </c>
       <c r="D86" s="11" t="n">
         <v>11</v>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>2879.913928738861</v>
+        <v>2902.103731622772</v>
       </c>
       <c r="D87" s="11" t="n">
         <v>11</v>
@@ -2919,16 +2919,16 @@
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>219.8612336573291</v>
+        <v>214.2454570626709</v>
       </c>
       <c r="D88" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G88" s="11" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>1761.312656176904</v>
+        <v>811.0862040329187</v>
       </c>
       <c r="D89" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G89" s="11" t="n">
         <v>0</v>
@@ -2971,20 +2971,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>2624.219972669092</v>
+        <v>1731.8254887675</v>
       </c>
       <c r="D90" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G90" s="11" t="n">
         <v>0</v>
@@ -2999,20 +2999,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>322.5943129077777</v>
+        <v>2577.566316607817</v>
       </c>
       <c r="D91" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G91" s="11" t="n">
         <v>0</v>
@@ -3027,20 +3027,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>2195.905074644911</v>
+        <v>322.7298132696295</v>
       </c>
       <c r="D92" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G92" s="11" t="n">
         <v>0</v>
@@ -3055,23 +3055,23 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>390.2940976528855</v>
+        <v>2100.303038965049</v>
       </c>
       <c r="D93" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F93" s="11" t="n">
         <v>29</v>
       </c>
       <c r="G93" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" s="11" t="n">
         <v>0</v>
@@ -3083,23 +3083,23 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>162.5985781732878</v>
+        <v>393.7361529581718</v>
       </c>
       <c r="D94" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H94" s="11" t="n">
         <v>0</v>
@@ -3111,20 +3111,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>3846.112996381999</v>
+        <v>162.6576418477171</v>
       </c>
       <c r="D95" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G95" s="11" t="n">
         <v>0</v>
@@ -3139,20 +3139,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>8291.830361264558</v>
+        <v>3732.094515884979</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>0</v>
@@ -3167,20 +3167,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>634.1852329913861</v>
+        <v>8436.467410853671</v>
       </c>
       <c r="D97" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G97" s="11" t="n">
         <v>0</v>
@@ -3195,20 +3195,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>939.9662103552466</v>
+        <v>639.4904876147277</v>
       </c>
       <c r="D98" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G98" s="11" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>1036.255762296291</v>
+        <v>1014.146299221291</v>
       </c>
       <c r="D99" s="11" t="n">
         <v>10</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>1145.916952313426</v>
+        <v>1114.702083856376</v>
       </c>
       <c r="D100" s="11" t="n">
         <v>10</v>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>521.4613664425248</v>
+        <v>505.145117332843</v>
       </c>
       <c r="D101" s="11" t="n">
         <v>10</v>
@@ -3307,17 +3307,17 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>528.9703031030274</v>
+        <v>1421.605073120117</v>
       </c>
       <c r="D102" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F102" s="11" t="n">
         <v>8</v>
@@ -3326,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -3335,11 +3335,11 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>1433.157122070312</v>
+        <v>871.5912788061523</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>10</v>
@@ -3348,13 +3348,13 @@
         <v>36</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G103" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>852.7544076913452</v>
+        <v>517.6589163793946</v>
       </c>
       <c r="D104" s="11" t="n">
         <v>10</v>
@@ -3376,7 +3376,7 @@
         <v>36</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G104" s="11" t="n">
         <v>0</v>
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>744.24392864</v>
+        <v>727.4175293538855</v>
       </c>
       <c r="D105" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F105" s="11" t="n">
         <v>12</v>

--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026. 10. 26</t>
+          <t>2026. 10. 27</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>26750.05765856</v>
+        <v>26867.6280814882</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>32</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>38947.72937999503</v>
+        <v>39548.45347218868</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>27</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>39161.47327730672</v>
+        <v>38744.43205169604</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>26</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>38803.13708250561</v>
+        <v>38425.23254410129</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>26</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2170.310888574184</v>
+        <v>2163.877668919184</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>21</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>50940.51282119751</v>
+        <v>52157.52</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>20</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>968.2457802997998</v>
+        <v>1006.27181219168</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>20</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>5</v>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>3112.898900146484</v>
+        <v>3193.962730102539</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>20</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>2637.349047534628</v>
+        <v>2680.968459317349</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>20</v>
@@ -871,26 +871,26 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>459.3678514995575</v>
+        <v>9543.503425934518</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>20</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -899,26 +899,26 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>9511.768319911156</v>
+        <v>180.7104419625647</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>20</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -927,23 +927,23 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>184.8372942846918</v>
+        <v>1635.362835877685</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>2</v>
@@ -955,26 +955,26 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>1643.427104612122</v>
+        <v>447.8926908348084</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>19</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>9928.804258792816</v>
+        <v>10224.67170495719</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>18</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1362.387538373012</v>
+        <v>1350.744951916711</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>18</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>7658.107824599078</v>
+        <v>7587.519083525202</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>18</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>5462.797771970386</v>
+        <v>5374.3209819</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>18</v>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>777.2498605477258</v>
+        <v>729.8470556613629</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>18</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1571.892909672452</v>
+        <v>1576.076322416085</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>18</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>16370.78437870505</v>
+        <v>16063.55519016503</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>17</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>2053.629861798981</v>
+        <v>2100.991633300885</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>17</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>299.1258794610123</v>
+        <v>304.3930430695974</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>16</v>
@@ -1239,16 +1239,16 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2246.321409733338</v>
+        <v>2385.37486904696</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>16</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G28" s="11" t="n">
         <v>2</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>5047.594071729071</v>
+        <v>5067.031930438952</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>16</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>819.9003250810025</v>
+        <v>822.4137622904981</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>16</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>341.4977174688294</v>
+        <v>345.072158770491</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>16</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>15355.81220010091</v>
+        <v>15713.35806761084</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>15</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>1178.144587377559</v>
+        <v>1174.232184448953</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>15</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>523.0303628749847</v>
+        <v>515.1615670714416</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>15</v>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>6057.996256948257</v>
+        <v>6131.610951574128</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>14</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>3824.541960595288</v>
+        <v>3821.510274418141</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>14</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>2741.954213109323</v>
+        <v>2660.757516500677</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>14</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>2173.972864174365</v>
+        <v>2235.394635396339</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>14</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>874.2826034024999</v>
+        <v>875.9286742488061</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>14</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>783.1656202697754</v>
+        <v>783.4608270263672</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>14</v>
@@ -1584,10 +1584,10 @@
         <v>38</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>2</v>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>1597.841268257532</v>
+        <v>1595.509620269304</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>14</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>1195.453619516731</v>
+        <v>1183.431266823269</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>14</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>662.1529505272612</v>
+        <v>660.5588444869852</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>14</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>880.5247083935889</v>
+        <v>877.3095726864111</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>14</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>644.5607844543457</v>
+        <v>647.8718792724609</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>14</v>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>3988.893363794285</v>
+        <v>3988.463016957617</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>14</v>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>446.1342997996143</v>
+        <v>450.2112103323047</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>14</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1566.432321406283</v>
+        <v>1551.732994224852</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>14</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>527.0979936218262</v>
+        <v>521.3504936218262</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>13</v>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1488.661980910358</v>
+        <v>1488.345765365857</v>
       </c>
       <c r="D50" s="11" t="n">
         <v>13</v>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>3752.754262951395</v>
+        <v>3686.422146198684</v>
       </c>
       <c r="D51" s="11" t="n">
         <v>13</v>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>2045.73116027832</v>
+        <v>2037.830305023193</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>12</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1207.493081007248</v>
+        <v>1186.648832160917</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>12</v>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>2170.61868515</v>
+        <v>2277.471704842631</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>12</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1894.990199466135</v>
+        <v>1976.687865883865</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>12</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>1942.868044166667</v>
+        <v>1906.262366155151</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>12</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1327.957800549168</v>
+        <v>1311.634910855557</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>12</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>11355.96976051111</v>
+        <v>11406.62115133458</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>12</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>854.7575141973188</v>
+        <v>834.7079493278238</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>12</v>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>402.0445815608826</v>
+        <v>404.9010581565125</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>12</v>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>50748.3437173645</v>
+        <v>50190.84497245483</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>12</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>351.0777128887489</v>
+        <v>361.1622888562489</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>12</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1327.513872802734</v>
+        <v>1328.516182006836</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>12</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>299.7725654219879</v>
+        <v>304.6298429390363</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>12</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>1934.825940613058</v>
+        <v>1967.684865741843</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>12</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>277.531965675</v>
+        <v>266.3729622235245</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>12</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>3500.114850377553</v>
+        <v>3497.345708869184</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>12</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>592.3840729435361</v>
+        <v>619.8951935614639</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>12</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>288.8325034812643</v>
+        <v>293.1335642459483</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>12</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>648.3750677274353</v>
+        <v>653.3284190774029</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>12</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>4574.655126994839</v>
+        <v>4551.115648253314</v>
       </c>
       <c r="D71" s="11" t="n">
         <v>12</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>897.9920412628969</v>
+        <v>894.5552553615556</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>12</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>159.7712077824683</v>
+        <v>158.2313982808228</v>
       </c>
       <c r="D73" s="11" t="n">
         <v>12</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>1710.06154928147</v>
+        <v>1733.768320065123</v>
       </c>
       <c r="D74" s="11" t="n">
         <v>12</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>935.9962258737778</v>
+        <v>935.7090705753324</v>
       </c>
       <c r="D75" s="11" t="n">
         <v>12</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>219.0130924155895</v>
+        <v>220.064797305883</v>
       </c>
       <c r="D76" s="11" t="n">
         <v>12</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>416.1836893980475</v>
+        <v>407.5446869255211</v>
       </c>
       <c r="D77" s="11" t="n">
         <v>12</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>573.2871790762915</v>
+        <v>585.3611107818542</v>
       </c>
       <c r="D78" s="11" t="n">
         <v>12</v>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>749.6613356899353</v>
+        <v>742.167891635108</v>
       </c>
       <c r="D79" s="11" t="n">
         <v>12</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>178.8725544287253</v>
+        <v>176.9125596225495</v>
       </c>
       <c r="D80" s="11" t="n">
         <v>12</v>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>942.3442317135205</v>
+        <v>954.7965936687671</v>
       </c>
       <c r="D81" s="11" t="n">
         <v>11</v>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>576.14072204</v>
+        <v>580.0050088424414</v>
       </c>
       <c r="D82" s="11" t="n">
         <v>11</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>223.0330639534536</v>
+        <v>224.9229557990464</v>
       </c>
       <c r="D83" s="11" t="n">
         <v>11</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>2345.605301493708</v>
+        <v>2339.750904068401</v>
       </c>
       <c r="D84" s="11" t="n">
         <v>11</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>877.0110400958911</v>
+        <v>877.62266116</v>
       </c>
       <c r="D85" s="11" t="n">
         <v>11</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>564.7600173273256</v>
+        <v>568.3525597775872</v>
       </c>
       <c r="D86" s="11" t="n">
         <v>11</v>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>2902.103731622772</v>
+        <v>2969.817750690842</v>
       </c>
       <c r="D87" s="11" t="n">
         <v>11</v>
@@ -2915,20 +2915,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>214.2454570626709</v>
+        <v>807.9945548652081</v>
       </c>
       <c r="D88" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G88" s="11" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>811.0862040329187</v>
+        <v>1746.398738973229</v>
       </c>
       <c r="D89" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G89" s="11" t="n">
         <v>0</v>
@@ -2971,20 +2971,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>1731.8254887675</v>
+        <v>2664.87513653608</v>
       </c>
       <c r="D90" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G90" s="11" t="n">
         <v>0</v>
@@ -2999,20 +2999,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>2577.566316607817</v>
+        <v>325.1237793524076</v>
       </c>
       <c r="D91" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G91" s="11" t="n">
         <v>0</v>
@@ -3027,20 +3027,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>322.7298132696295</v>
+        <v>2112.574050854505</v>
       </c>
       <c r="D92" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G92" s="11" t="n">
         <v>0</v>
@@ -3055,23 +3055,23 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>2100.303038965049</v>
+        <v>394.2796426492786</v>
       </c>
       <c r="D93" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F93" s="11" t="n">
         <v>29</v>
       </c>
       <c r="G93" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H93" s="11" t="n">
         <v>0</v>
@@ -3083,23 +3083,23 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>393.7361529581718</v>
+        <v>162.5395144988586</v>
       </c>
       <c r="D94" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H94" s="11" t="n">
         <v>0</v>
@@ -3111,20 +3111,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>162.6576418477171</v>
+        <v>3706.598759845723</v>
       </c>
       <c r="D95" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G95" s="11" t="n">
         <v>0</v>
@@ -3139,20 +3139,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>3732.094515884979</v>
+        <v>8673.013881401772</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>0</v>
@@ -3167,20 +3167,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>8436.467410853671</v>
+        <v>647.504073704307</v>
       </c>
       <c r="D97" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G97" s="11" t="n">
         <v>0</v>
@@ -3195,26 +3195,26 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>639.4904876147277</v>
+        <v>1008.486327053727</v>
       </c>
       <c r="D98" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -3223,23 +3223,23 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>1014.146299221291</v>
+        <v>1112.121283310604</v>
       </c>
       <c r="D99" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H99" s="11" t="n">
         <v>2</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>1114.702083856376</v>
+        <v>520.8034641014709</v>
       </c>
       <c r="D100" s="11" t="n">
         <v>10</v>
@@ -3264,7 +3264,7 @@
         <v>38</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G100" s="11" t="n">
         <v>0</v>
@@ -3279,26 +3279,26 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>505.145117332843</v>
+        <v>515.9300321557618</v>
       </c>
       <c r="D101" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G101" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>1421.605073120117</v>
+        <v>1444.165412139893</v>
       </c>
       <c r="D102" s="11" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>871.5912788061523</v>
+        <v>887.2336650790405</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>10</v>
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>517.6589163793946</v>
+        <v>741.058322821045</v>
       </c>
       <c r="D104" s="11" t="n">
         <v>10</v>
@@ -3376,7 +3376,7 @@
         <v>36</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G104" s="11" t="n">
         <v>0</v>
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>727.4175293538855</v>
+        <v>736.5588258035242</v>
       </c>
       <c r="D105" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F105" s="11" t="n">
         <v>12</v>

--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026. 10. 27</t>
+          <t>2026. 10. 28</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>26867.6280814882</v>
+        <v>27300.16030907633</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>32</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>39548.45347218868</v>
+        <v>39454.15212634442</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>27</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>38744.43205169604</v>
+        <v>39206.72343901663</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>26</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>38425.23254410129</v>
+        <v>38748.10088285414</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>26</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2163.877668919184</v>
+        <v>2133.384270578895</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>21</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>52157.52</v>
+        <v>52625.97238952637</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>20</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1006.27181219168</v>
+        <v>1008.35450869624</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>20</v>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>3193.962730102539</v>
+        <v>3285.906099853516</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>20</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>2680.968459317349</v>
+        <v>2744.350051035558</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>20</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>9543.503425934518</v>
+        <v>9466.545990549328</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>20</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>180.7104419625647</v>
+        <v>188.9856287574353</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>20</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>1635.362835877685</v>
+        <v>1600.211590979614</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>19</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>447.8926908348084</v>
+        <v>449.8152330013275</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>19</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>10224.67170495719</v>
+        <v>10508.20633426175</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>18</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1350.744951916711</v>
+        <v>1343.596022660205</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>18</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>7587.519083525202</v>
+        <v>7544.339568814188</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>18</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>5374.3209819</v>
+        <v>5342.346405220385</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>18</v>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>729.8470556613629</v>
+        <v>739.0329507686371</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>18</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1576.076322416085</v>
+        <v>1575.003749009104</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>18</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>16063.55519016503</v>
+        <v>15857.22285598728</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>17</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>2100.991633300885</v>
+        <v>2188.974891707192</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>17</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>304.3930430695974</v>
+        <v>328.5503521282438</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>16</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2385.37486904696</v>
+        <v>2420.084822539459</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>16</v>
@@ -1263,26 +1263,26 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>5067.031930438952</v>
+        <v>825.1066280030012</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>16</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G29" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1291,20 +1291,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>822.4137622904981</v>
+        <v>345.9657752938293</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>16</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" s="11" t="n">
         <v>0</v>
@@ -1319,20 +1319,20 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>345.072158770491</v>
+        <v>16341.56647586416</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" s="11" t="n">
         <v>0</v>
@@ -1347,26 +1347,26 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>15713.35806761084</v>
+        <v>5060.847451366571</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>15</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>1174.232184448953</v>
+        <v>1156.16592675837</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>15</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>515.1615670714416</v>
+        <v>507.5194673750153</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>15</v>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>6131.610951574128</v>
+        <v>6303.776755817918</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>14</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>3821.510274418141</v>
+        <v>3957.018412784071</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>14</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>2660.757516500677</v>
+        <v>2603.295104496203</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>14</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>2235.394635396339</v>
+        <v>2358.49009176</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>14</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>875.9286742488061</v>
+        <v>882.9162736971454</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>14</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>783.4608270263672</v>
+        <v>798.2208270263671</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>14</v>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>1595.509620269304</v>
+        <v>1575.196133084304</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>14</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>1183.431266823269</v>
+        <v>1165.52566214173</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>14</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>660.5588444869852</v>
+        <v>653.0228443177389</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>14</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>877.3095726864111</v>
+        <v>856.5743647703833</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>14</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>647.8718792724609</v>
+        <v>683.7846077728271</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>14</v>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>3988.463016957617</v>
+        <v>3923.064412897738</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>14</v>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>450.2112103323047</v>
+        <v>497.3644488930761</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>14</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1551.732994224852</v>
+        <v>1544.296845377138</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>14</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>521.3504936218262</v>
+        <v>505.9890127563477</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>13</v>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1488.345765365857</v>
+        <v>1329.244241747571</v>
       </c>
       <c r="D50" s="11" t="n">
         <v>13</v>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>3686.422146198684</v>
+        <v>3683.63962408692</v>
       </c>
       <c r="D51" s="11" t="n">
         <v>13</v>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>2037.830305023193</v>
+        <v>1982.524694976807</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>12</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1186.648832160917</v>
+        <v>1163.402479080917</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>12</v>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>2277.471704842631</v>
+        <v>2383.898662330793</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>12</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1976.687865883865</v>
+        <v>2061.099234953029</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>12</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>1906.262366155151</v>
+        <v>1903.327030038333</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>12</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1311.634910855557</v>
+        <v>1320.60752657333</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>12</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>11406.62115133458</v>
+        <v>11431.32256244903</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>12</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>834.7079493278238</v>
+        <v>850.1721753985491</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>12</v>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>404.9010581565125</v>
+        <v>390.941076282605</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>12</v>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>50190.84497245483</v>
+        <v>50656.39967075806</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>12</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>361.1622888562489</v>
+        <v>372.9948467070316</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>12</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1328.516182006836</v>
+        <v>1323.445618408203</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>12</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>304.6298429390363</v>
+        <v>303.4656897284335</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>12</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>1967.684865741843</v>
+        <v>1972.520683278257</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>12</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>266.3729622235245</v>
+        <v>262.5442904632462</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>12</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>3497.345708869184</v>
+        <v>3508.422010822789</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>12</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>619.8951935614639</v>
+        <v>639.2361810899999</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>12</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>293.1335642459483</v>
+        <v>294.6223941857375</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>12</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>653.3284190774029</v>
+        <v>648.8896812373059</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>12</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>4551.115648253314</v>
+        <v>4476.967068441466</v>
       </c>
       <c r="D71" s="11" t="n">
         <v>12</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>894.5552553615556</v>
+        <v>917.5852890595712</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>12</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>158.2313982808228</v>
+        <v>155.0534978191772</v>
       </c>
       <c r="D73" s="11" t="n">
         <v>12</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>1733.768320065123</v>
+        <v>1633.680872135245</v>
       </c>
       <c r="D74" s="11" t="n">
         <v>12</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>935.7090705753324</v>
+        <v>947.0535125947231</v>
       </c>
       <c r="D75" s="11" t="n">
         <v>12</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>220.064797305883</v>
+        <v>221.0371262426468</v>
       </c>
       <c r="D76" s="11" t="n">
         <v>12</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>407.5446869255211</v>
+        <v>426.4064893089842</v>
       </c>
       <c r="D77" s="11" t="n">
         <v>12</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>585.3611107818542</v>
+        <v>583.3487888309271</v>
       </c>
       <c r="D78" s="11" t="n">
         <v>12</v>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>742.167891635108</v>
+        <v>734.7541818926295</v>
       </c>
       <c r="D79" s="11" t="n">
         <v>12</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>176.9125596225495</v>
+        <v>176.6233935637253</v>
       </c>
       <c r="D80" s="11" t="n">
         <v>12</v>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>954.7965936687671</v>
+        <v>986.1051003647534</v>
       </c>
       <c r="D81" s="11" t="n">
         <v>11</v>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>580.0050088424414</v>
+        <v>572.5844587178638</v>
       </c>
       <c r="D82" s="11" t="n">
         <v>11</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>224.9229557990464</v>
+        <v>226.3583434944166</v>
       </c>
       <c r="D83" s="11" t="n">
         <v>11</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>2339.750904068401</v>
+        <v>2344.775570963504</v>
       </c>
       <c r="D84" s="11" t="n">
         <v>11</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>877.62266116</v>
+        <v>906.2447352110694</v>
       </c>
       <c r="D85" s="11" t="n">
         <v>11</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>568.3525597775872</v>
+        <v>570.6145027515407</v>
       </c>
       <c r="D86" s="11" t="n">
         <v>11</v>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>2969.817750690842</v>
+        <v>3191.525625570297</v>
       </c>
       <c r="D87" s="11" t="n">
         <v>11</v>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>807.9945548652081</v>
+        <v>788.1765184152081</v>
       </c>
       <c r="D88" s="11" t="n">
         <v>11</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>1746.398738973229</v>
+        <v>1759.392292489255</v>
       </c>
       <c r="D89" s="11" t="n">
         <v>11</v>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>2664.87513653608</v>
+        <v>2626.011388771315</v>
       </c>
       <c r="D90" s="11" t="n">
         <v>11</v>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>325.1237793524076</v>
+        <v>321.1940965540741</v>
       </c>
       <c r="D91" s="11" t="n">
         <v>11</v>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>2112.574050854505</v>
+        <v>2098.224344080149</v>
       </c>
       <c r="D92" s="11" t="n">
         <v>11</v>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>394.2796426492786</v>
+        <v>392.5767211838932</v>
       </c>
       <c r="D93" s="11" t="n">
         <v>11</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>162.5395144988586</v>
+        <v>160.5904583036683</v>
       </c>
       <c r="D94" s="11" t="n">
         <v>11</v>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>3706.598759845723</v>
+        <v>3690.605999572521</v>
       </c>
       <c r="D95" s="11" t="n">
         <v>11</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>8673.013881401772</v>
+        <v>9146.104829730592</v>
       </c>
       <c r="D96" s="11" t="n">
         <v>10</v>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>647.504073704307</v>
+        <v>664.1248008231313</v>
       </c>
       <c r="D97" s="11" t="n">
         <v>10</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>1008.486327053727</v>
+        <v>995.3385915349451</v>
       </c>
       <c r="D98" s="11" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>1112.121283310604</v>
+        <v>1111.896813761376</v>
       </c>
       <c r="D99" s="11" t="n">
         <v>10</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>520.8034641014709</v>
+        <v>535.8696134321076</v>
       </c>
       <c r="D100" s="11" t="n">
         <v>10</v>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>515.9300321557618</v>
+        <v>508.3432525854492</v>
       </c>
       <c r="D101" s="11" t="n">
         <v>10</v>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>1444.165412139893</v>
+        <v>1491.848647399902</v>
       </c>
       <c r="D102" s="11" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>887.2336650790405</v>
+        <v>944.8182674209595</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>10</v>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>741.058322821045</v>
+        <v>784.6105754663134</v>
       </c>
       <c r="D104" s="11" t="n">
         <v>10</v>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>736.5588258035242</v>
+        <v>726.6085809056476</v>
       </c>
       <c r="D105" s="11" t="n">
         <v>10</v>

--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026. 10. 28</t>
+          <t>2026. 10. 29</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>27300.16030907633</v>
+        <v>27461.95501265633</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>32</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>39454.15212634442</v>
+        <v>39430.38983691003</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>27</v>
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>39206.72343901663</v>
+        <v>39733.83706393026</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>26</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>10</v>
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>38748.10088285414</v>
+        <v>39366.93901900026</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>26</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2133.384270578895</v>
+        <v>2164.392436434302</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>21</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>52625.97238952637</v>
+        <v>52007.80977905273</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>20</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1008.35450869624</v>
+        <v>999.7007874681201</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>20</v>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>3285.906099853516</v>
+        <v>3226.928120117188</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>20</v>
@@ -828,13 +828,13 @@
         <v>64</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>2744.350051035558</v>
+        <v>2730.424687174814</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>20</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>9466.545990549328</v>
+        <v>9422.910144105108</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>20</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>188.9856287574353</v>
+        <v>189.4692395237176</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>20</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>1600.211590979614</v>
+        <v>1552.137071081543</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>19</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>449.8152330013275</v>
+        <v>451.8579139995575</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>19</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>10508.20633426175</v>
+        <v>11124.4922263665</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>18</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1343.596022660205</v>
+        <v>1333.178922409313</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>18</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>7544.339568814188</v>
+        <v>7520.685282138672</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>18</v>
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>5342.346405220385</v>
+        <v>5346.376243427038</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>18</v>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>739.0329507686371</v>
+        <v>734.3928277662411</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>18</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>19</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1575.003749009104</v>
+        <v>1588.412144171604</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>18</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>15857.22285598728</v>
+        <v>15660.34640025587</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>17</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>2188.974891707192</v>
+        <v>2261.590103761924</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>17</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>328.5503521282438</v>
+        <v>352.5973513417561</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>16</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2420.084822539459</v>
+        <v>2519.408559085541</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>16</v>
@@ -1248,13 +1248,13 @@
         <v>41</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G28" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>825.1066280030012</v>
+        <v>835.1601713884994</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>16</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>345.9657752938293</v>
+        <v>343.7723799638443</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>16</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>16341.56647586416</v>
+        <v>16794.1071115128</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>15</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>5060.847451366571</v>
+        <v>5053.778550801452</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>15</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>1156.16592675837</v>
+        <v>1166.06205984</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>15</v>
@@ -1388,7 +1388,7 @@
         <v>30</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G33" s="11" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>507.5194673750153</v>
+        <v>514.5787189285584</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>15</v>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>6303.776755817918</v>
+        <v>6408.918828750871</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>14</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>3957.018412784071</v>
+        <v>4381.731557233639</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>14</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>2603.295104496203</v>
+        <v>2581.226275042745</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>14</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>2358.49009176</v>
+        <v>2354.958678141409</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>14</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>882.9162736971454</v>
+        <v>873.3419768445242</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>14</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>798.2208270263671</v>
+        <v>793.35</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>14</v>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>1575.196133084304</v>
+        <v>1569.190363313544</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>14</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>1165.52566214173</v>
+        <v>1150.433807884422</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>14</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>653.0228443177389</v>
+        <v>614.9080923044975</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>14</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>856.5743647703833</v>
+        <v>856.2015881999999</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>14</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>683.7846077728271</v>
+        <v>700.2552285003662</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>14</v>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>3923.064412897738</v>
+        <v>3945.811265004052</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>14</v>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>497.3644488930761</v>
+        <v>515.5977502653809</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>14</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1544.296845377138</v>
+        <v>1534.958416688997</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>14</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>505.9890127563477</v>
+        <v>506.5742102050781</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>13</v>
@@ -1851,20 +1851,20 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1329.244241747571</v>
+        <v>3654.108676921842</v>
       </c>
       <c r="D50" s="11" t="n">
         <v>13</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G50" s="11" t="n">
         <v>0</v>
@@ -1879,26 +1879,26 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>3683.63962408692</v>
+        <v>1992.565305023193</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E51" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="F51" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F51" s="11" t="n">
-        <v>9</v>
-      </c>
       <c r="G51" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -1907,26 +1907,26 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>1982.524694976807</v>
+        <v>1111.592330044251</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G52" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1935,17 +1935,17 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1163.402479080917</v>
+        <v>2338.488819281716</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F53" s="11" t="n">
         <v>14</v>
@@ -1963,20 +1963,20 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>2383.898662330793</v>
+        <v>2075.248463719548</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G54" s="11" t="n">
         <v>0</v>
@@ -1991,23 +1991,23 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>2061.099234953029</v>
+        <v>1882.779413749091</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G55" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H55" s="11" t="n">
         <v>0</v>
@@ -2019,26 +2019,26 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>1903.327030038333</v>
+        <v>1342.557174523611</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G56" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H56" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2047,20 +2047,20 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1320.60752657333</v>
+        <v>11488.30496891861</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G57" s="11" t="n">
         <v>2</v>
@@ -2075,20 +2075,20 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>11431.32256244903</v>
+        <v>822.0309249476812</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G58" s="11" t="n">
         <v>2</v>
@@ -2103,11 +2103,11 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>850.1721753985491</v>
+        <v>389.7278423554413</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>12</v>
@@ -2131,26 +2131,26 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>390.941076282605</v>
+        <v>50179.16713433227</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H60" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -2159,11 +2159,11 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>50656.39967075806</v>
+        <v>1324.500824879269</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>12</v>
@@ -2172,13 +2172,13 @@
         <v>37</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>372.9948467070316</v>
+        <v>377.2975950164072</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>12</v>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1323.445618408203</v>
+        <v>1302.607631072998</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F63" s="11" t="n">
         <v>2</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>303.4656897284335</v>
+        <v>310.9723820649396</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>12</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>1972.520683278257</v>
+        <v>1974.008568919572</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>12</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>262.5442904632462</v>
+        <v>259.1580930985245</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>12</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>3508.422010822789</v>
+        <v>3520.190466113552</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>12</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>639.2361810899999</v>
+        <v>634.6720156969519</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>12</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>294.6223941857375</v>
+        <v>295.780366016159</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>12</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>648.8896812373059</v>
+        <v>655.9444801511692</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>12</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>4476.967068441466</v>
+        <v>4495.994644144619</v>
       </c>
       <c r="D71" s="11" t="n">
         <v>12</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>917.5852890595712</v>
+        <v>914.3964361477463</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>12</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>155.0534978191772</v>
+        <v>147.7967543664716</v>
       </c>
       <c r="D73" s="11" t="n">
         <v>12</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>1633.680872135245</v>
+        <v>1663.092617661285</v>
       </c>
       <c r="D74" s="11" t="n">
         <v>12</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>947.0535125947231</v>
+        <v>956.3876484061115</v>
       </c>
       <c r="D75" s="11" t="n">
         <v>12</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>221.0371262426468</v>
+        <v>220.7394702017638</v>
       </c>
       <c r="D76" s="11" t="n">
         <v>12</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>426.4064893089842</v>
+        <v>425.1106375649736</v>
       </c>
       <c r="D77" s="11" t="n">
         <v>12</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>583.3487888309271</v>
+        <v>590.0006332046356</v>
       </c>
       <c r="D78" s="11" t="n">
         <v>12</v>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>734.7541818926295</v>
+        <v>730.9277863723273</v>
       </c>
       <c r="D79" s="11" t="n">
         <v>12</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>176.6233935637253</v>
+        <v>168.0105618635953</v>
       </c>
       <c r="D80" s="11" t="n">
         <v>12</v>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>986.1051003647534</v>
+        <v>994.2750846488563</v>
       </c>
       <c r="D81" s="11" t="n">
         <v>11</v>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>572.5844587178638</v>
+        <v>577.4568184806103</v>
       </c>
       <c r="D82" s="11" t="n">
         <v>11</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>226.3583434944166</v>
+        <v>211.9880188808065</v>
       </c>
       <c r="D83" s="11" t="n">
         <v>11</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>2344.775570963504</v>
+        <v>2342.516813182398</v>
       </c>
       <c r="D84" s="11" t="n">
         <v>11</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>906.2447352110694</v>
+        <v>908.4464403934802</v>
       </c>
       <c r="D85" s="11" t="n">
         <v>11</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>570.6145027515407</v>
+        <v>575.7372219102616</v>
       </c>
       <c r="D86" s="11" t="n">
         <v>11</v>
@@ -2887,20 +2887,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>3191.525625570297</v>
+        <v>819.7088782982401</v>
       </c>
       <c r="D87" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E87" s="11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G87" s="11" t="n">
         <v>0</v>
@@ -2915,20 +2915,20 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>788.1765184152081</v>
+        <v>3139.579832554703</v>
       </c>
       <c r="D88" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G88" s="11" t="n">
         <v>0</v>
@@ -2943,20 +2943,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>1759.392292489255</v>
+        <v>779.5094337</v>
       </c>
       <c r="D89" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G89" s="11" t="n">
         <v>0</v>
@@ -2971,20 +2971,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>2626.011388771315</v>
+        <v>1793.200183671176</v>
       </c>
       <c r="D90" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G90" s="11" t="n">
         <v>0</v>
@@ -2999,20 +2999,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>321.1940965540741</v>
+        <v>2642.744319785211</v>
       </c>
       <c r="D91" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G91" s="11" t="n">
         <v>0</v>
@@ -3027,20 +3027,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>2098.224344080149</v>
+        <v>342.468514887963</v>
       </c>
       <c r="D92" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G92" s="11" t="n">
         <v>0</v>
@@ -3055,23 +3055,23 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>392.5767211838932</v>
+        <v>2131.953102400099</v>
       </c>
       <c r="D93" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F93" s="11" t="n">
         <v>29</v>
       </c>
       <c r="G93" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" s="11" t="n">
         <v>0</v>
@@ -3083,23 +3083,23 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>160.5904583036683</v>
+        <v>396.0550165067291</v>
       </c>
       <c r="D94" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H94" s="11" t="n">
         <v>0</v>
@@ -3111,20 +3111,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>3690.605999572521</v>
+        <v>157.991712955</v>
       </c>
       <c r="D95" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G95" s="11" t="n">
         <v>0</v>
@@ -3139,20 +3139,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>9146.104829730592</v>
+        <v>3668.123474792169</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>0</v>
@@ -3167,20 +3167,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>664.1248008231313</v>
+        <v>9442.888672800147</v>
       </c>
       <c r="D97" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G97" s="11" t="n">
         <v>0</v>
@@ -3195,26 +3195,26 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>995.3385915349451</v>
+        <v>666.9444273786756</v>
       </c>
       <c r="D98" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -3223,23 +3223,23 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>1111.896813761376</v>
+        <v>978.9775348812638</v>
       </c>
       <c r="D99" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H99" s="11" t="n">
         <v>2</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>535.8696134321076</v>
+        <v>1112.442735121158</v>
       </c>
       <c r="D100" s="11" t="n">
         <v>10</v>
@@ -3264,7 +3264,7 @@
         <v>38</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G100" s="11" t="n">
         <v>0</v>
@@ -3279,26 +3279,26 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>508.3432525854492</v>
+        <v>528.6325872910538</v>
       </c>
       <c r="D101" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G101" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -3307,17 +3307,17 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>1491.848647399902</v>
+        <v>508.059720523313</v>
       </c>
       <c r="D102" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F102" s="11" t="n">
         <v>8</v>
@@ -3326,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3335,11 +3335,11 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>944.8182674209595</v>
+        <v>1525.945938964844</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>10</v>
@@ -3348,13 +3348,13 @@
         <v>36</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G103" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>784.6105754663134</v>
+        <v>943.1108442678833</v>
       </c>
       <c r="D104" s="11" t="n">
         <v>10</v>
@@ -3376,7 +3376,7 @@
         <v>36</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G104" s="11" t="n">
         <v>0</v>
@@ -3391,11 +3391,11 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>726.6085809056476</v>
+        <v>827.8820234694775</v>
       </c>
       <c r="D105" s="11" t="n">
         <v>10</v>
@@ -3404,7 +3404,7 @@
         <v>36</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G105" s="11" t="n">
         <v>0</v>

--- a/docs/strong_buy_top100.xlsx
+++ b/docs/strong_buy_top100.xlsx
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026. 10. 29</t>
+          <t>2026. 10. 30</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>27461.95501265633</v>
+        <v>26295.95313300004</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>32</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>39430.38983691003</v>
+        <v>39365.78795371379</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>27</v>
@@ -675,20 +675,20 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>39733.83706393026</v>
+        <v>34527.55291062638</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>0</v>
@@ -703,17 +703,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>39366.93901900026</v>
+        <v>34711.00193309138</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>10</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2164.392436434302</v>
+        <v>2147.280048592848</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>21</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>52007.80977905273</v>
+        <v>51592.48108428955</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>20</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>999.7007874681201</v>
+        <v>954.5650306518799</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>20</v>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>3226.928120117188</v>
+        <v>3114.749011282964</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>20</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>2730.424687174814</v>
+        <v>2674.005777386977</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>20</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>9422.910144105108</v>
+        <v>9619.667317212499</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>20</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>189.4692395237176</v>
+        <v>190.1033073372565</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>20</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>1552.137071081543</v>
+        <v>1133.836436469421</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>19</v>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>451.8579139995575</v>
+        <v>462.3117341651916</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>19</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>11124.4922263665</v>
+        <v>10570.5478637335</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>18</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1333.178922409313</v>
+        <v>1342.778979911608</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>18</v>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>7520.685282138672</v>
+        <v>7673.017215572899</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>18</v>
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>5346.376243427038</v>
+        <v>5568.795295514808</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>18</v>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>734.3928277662411</v>
+        <v>775.59922066</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>18</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1588.412144171604</v>
+        <v>1565.46472093338</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>18</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>15660.34640025587</v>
+        <v>15967.93416331825</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>17</v>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>2261.590103761924</v>
+        <v>1962.231619112654</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>17</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>352.5973513417561</v>
+        <v>335.0033413121587</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>16</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2519.408559085541</v>
+        <v>2443.260371931122</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>16</v>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>835.1601713884994</v>
+        <v>860.1144301388337</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>16</v>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>343.7723799638443</v>
+        <v>355.8604864908233</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>16</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>16794.1071115128</v>
+        <v>16469.02303425</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>15</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>5053.778550801452</v>
+        <v>5138.600504050291</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>15</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>1166.06205984</v>
+        <v>1195.788970905</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>15</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>514.5787189285584</v>
+        <v>502.4679191607208</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>15</v>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>6408.918828750871</v>
+        <v>6458.444914501743</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>14</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>4381.731557233639</v>
+        <v>4230.762929533142</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>14</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>2581.226275042745</v>
+        <v>2583.724537189661</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>14</v>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>2354.958678141409</v>
+        <v>2323.428061941408</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>14</v>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>873.3419768445242</v>
+        <v>856.3434452835727</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>14</v>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>793.35</v>
+        <v>794.251555025482</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>14</v>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>1569.190363313544</v>
+        <v>1585.370557828608</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>14</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>1150.433807884422</v>
+        <v>1155.293957736347</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>14</v>
@@ -1659,16 +1659,16 @@
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>614.9080923044975</v>
+        <v>618.6760647472611</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G43" s="11" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>856.2015881999999</v>
+        <v>862.0437186787049</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>14</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>700.2552285003662</v>
+        <v>727.7628103637695</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>14</v>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>3945.811265004052</v>
+        <v>3993.025734218636</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>14</v>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>515.5977502653809</v>
+        <v>503.8527748407715</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>14</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1534.958416688997</v>
+        <v>1547.236684425855</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>14</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>506.5742102050781</v>
+        <v>505.2156910705567</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>13</v>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>3654.108676921842</v>
+        <v>3688.307018678605</v>
       </c>
       <c r="D50" s="11" t="n">
         <v>13</v>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>1992.565305023193</v>
+        <v>1900.306949768066</v>
       </c>
       <c r="D51" s="11" t="n">
         <v>12</v>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>1111.592330044251</v>
+        <v>1130.301631117248</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>12</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>2338.488819281716</v>
+        <v>2349.935265862576</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>12</v>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>2075.248463719548</v>
+        <v>2099.525240836894</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>12</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1882.779413749091</v>
+        <v>1915.068506241363</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>12</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>1342.557174523611</v>
+        <v>1368.6889896</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>12</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>11488.30496891861</v>
+        <v>12249.85125880139</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>12</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>822.0309249476812</v>
+        <v>824.7599276273245</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>12</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>389.7278423554413</v>
+        <v>371.4984478065124</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>12</v>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>50179.16713433227</v>
+        <v>50920.55397245484</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>12</v>
@@ -2144,7 +2144,7 @@
         <v>37</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G60" s="11" t="n">
         <v>6</v>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>1324.500824879269</v>
+        <v>1368.164773042694</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>12</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>377.2975950164072</v>
+        <v>387.7855632553122</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>12</v>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1302.607631072998</v>
+        <v>1335.453350616455</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>12</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>310.9723820649396</v>
+        <v>232.82786532</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>12</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>1974.008568919572</v>
+        <v>2053.489739763586</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>12</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>259.1580930985245</v>
+        <v>249.345888702951</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>12</v>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>3520.190466113552</v>
+        <v>3540.266345929421</v>
       </c>
       <c r="D67" s="11" t="n">
         <v>12</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>634.6720156969519</v>
+        <v>670.46094808</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>12</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>295.780366016159</v>
+        <v>296.9383693989464</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>12</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>655.9444801511692</v>
+        <v>669.8181698274353</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>12</v>
@@ -2443,13 +2443,13 @@
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>4495.994644144619</v>
+        <v>4540.327069699839</v>
       </c>
       <c r="D71" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F71" s="11" t="n">
         <v>8</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>914.3964361477463</v>
+        <v>937.4264157827463</v>
       </c>
       <c r="D72" s="11" t="n">
         <v>12</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>147.7967543664716</v>
+        <v>153.1328351687659</v>
       </c>
       <c r="D73" s="11" t="n">
         <v>12</v>
@@ -2527,16 +2527,16 @@
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>1663.092617661285</v>
+        <v>1706.792728096771</v>
       </c>
       <c r="D74" s="11" t="n">
         <v>12</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G74" s="11" t="n">
         <v>0</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>956.3876484061115</v>
+        <v>949.7819809474446</v>
       </c>
       <c r="D75" s="11" t="n">
         <v>12</v>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>220.7394702017638</v>
+        <v>233.8361997458807</v>
       </c>
       <c r="D76" s="11" t="n">
         <v>12</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>425.1106375649736</v>
+        <v>491.7748855104156</v>
       </c>
       <c r="D77" s="11" t="n">
         <v>12</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>590.0006332046356</v>
+        <v>590.2800963026822</v>
       </c>
       <c r="D78" s="11" t="n">
         <v>12</v>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>730.9277863723273</v>
+        <v>742.6462366897409</v>
       </c>
       <c r="D79" s="11" t="n">
         <v>12</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>168.0105618635953</v>
+        <v>170.4527547003268</v>
       </c>
       <c r="D80" s="11" t="n">
         <v>12</v>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>994.2750846488563</v>
+        <v>1022.899810617781</v>
       </c>
       <c r="D81" s="11" t="n">
         <v>11</v>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>577.4568184806103</v>
+        <v>578.0448361163379</v>
       </c>
       <c r="D82" s="11" t="n">
         <v>11</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>211.9880188808065</v>
+        <v>208.8778311698071</v>
       </c>
       <c r="D83" s="11" t="n">
         <v>11</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>2342.516813182398</v>
+        <v>2319.421661998504</v>
       </c>
       <c r="D84" s="11" t="n">
         <v>11</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>908.4464403934802</v>
+        <v>915.907769438302</v>
       </c>
       <c r="D85" s="11" t="n">
         <v>11</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>575.7372219102616</v>
+        <v>602.8808421407848</v>
       </c>
       <c r="D86" s="11" t="n">
         <v>11</v>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>819.7088782982401</v>
+        <v>843.3965939220398</v>
       </c>
       <c r="D87" s="11" t="n">
         <v>11</v>
@@ -2915,17 +2915,17 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>3139.579832554703</v>
+        <v>2184.97227397407</v>
       </c>
       <c r="D88" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F88" s="11" t="n">
         <v>19</v>
@@ -2943,20 +2943,20 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>779.5094337</v>
+        <v>3023.353269616089</v>
       </c>
       <c r="D89" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G89" s="11" t="n">
         <v>0</v>
@@ -2971,20 +2971,20 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>1793.200183671176</v>
+        <v>788.5200439493756</v>
       </c>
       <c r="D90" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G90" s="11" t="n">
         <v>0</v>
@@ -2999,20 +2999,20 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>2642.744319785211</v>
+        <v>1821.634156937649</v>
       </c>
       <c r="D91" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G91" s="11" t="n">
         <v>0</v>
@@ -3027,20 +3027,20 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>342.468514887963</v>
+        <v>2690.784370348685</v>
       </c>
       <c r="D92" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G92" s="11" t="n">
         <v>0</v>
@@ -3055,20 +3055,20 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>2131.953102400099</v>
+        <v>345.523722171309</v>
       </c>
       <c r="D93" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G93" s="11" t="n">
         <v>0</v>
@@ -3083,11 +3083,11 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>396.0550165067291</v>
+        <v>2170.643880169654</v>
       </c>
       <c r="D94" s="11" t="n">
         <v>11</v>
@@ -3099,7 +3099,7 @@
         <v>29</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H94" s="11" t="n">
         <v>0</v>
@@ -3111,23 +3111,23 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>157.991712955</v>
+        <v>394.2434026317291</v>
       </c>
       <c r="D95" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G95" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H95" s="11" t="n">
         <v>0</v>
@@ -3139,20 +3139,20 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>3668.123474792169</v>
+        <v>157.3420238015219</v>
       </c>
       <c r="D96" s="11" t="n">
         <v>11</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>0</v>
@@ -3167,20 +3167,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>9442.888672800147</v>
+        <v>3722.127864463946</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G97" s="11" t="n">
         <v>0</v>
@@ -3195,20 +3195,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>666.9444273786756</v>
+        <v>9246.664853908966</v>
       </c>
       <c r="D98" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G98" s="11" t="n">
         <v>0</v>
@@ -3223,26 +3223,26 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>978.9775348812638</v>
+        <v>678.5937851420791</v>
       </c>
       <c r="D99" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H99" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -3251,23 +3251,23 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>1112.442735121158</v>
+        <v>981.3653496962729</v>
       </c>
       <c r="D100" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" s="11" t="n">
         <v>2</v>
@@ -3279,11 +3279,11 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>528.6325872910538</v>
+        <v>1162.233547740232</v>
       </c>
       <c r="D101" s="11" t="n">
         <v>10</v>
@@ -3292,7 +3292,7 @@
         <v>38</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G101" s="11" t="n">
         <v>0</v>
@@ -3307,26 +3307,26 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>508.059720523313</v>
+        <v>537.1196630164216</v>
       </c>
       <c r="D102" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G102" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H102" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -3335,17 +3335,17 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>1525.945938964844</v>
+        <v>504.8859211932519</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>10</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F103" s="11" t="n">
         <v>8</v>
@@ -3354,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3363,11 +3363,11 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>943.1108442678833</v>
+        <v>1529.208484741211</v>
       </c>
       <c r="D104" s="11" t="n">
         <v>10</v>
@@ -3376,13 +3376,13 @@
         <v>36</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G104" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H104" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>827.8820234694775</v>
+        <v>832.9365623147461</v>
       </c>
       <c r="D105" s="11" t="n">
         <v>10</v>
